--- a/data/H131_20260618_18.xlsx
+++ b/data/H131_20260618_18.xlsx
@@ -669,7 +669,7 @@
         <v>667.0</v>
       </c>
       <c r="J5" s="2">
-        <v>491.0</v>
+        <v>501.0</v>
       </c>
       <c r="K5" s="2">
         <v>1.0</v>
@@ -681,13 +681,13 @@
         <v>0.0</v>
       </c>
       <c r="N5" s="2">
-        <v>491.0</v>
+        <v>501.0</v>
       </c>
       <c r="O5" s="2">
-        <v>237.0</v>
+        <v>243.0</v>
       </c>
       <c r="P5" s="2">
-        <v>253.0</v>
+        <v>257.0</v>
       </c>
       <c r="Q5" s="2">
         <v>1.0</v>
@@ -740,7 +740,7 @@
         <v>929.0</v>
       </c>
       <c r="J6" s="2">
-        <v>679.0</v>
+        <v>693.0</v>
       </c>
       <c r="K6" s="2">
         <v>1.0</v>
@@ -752,13 +752,13 @@
         <v>0.0</v>
       </c>
       <c r="N6" s="2">
-        <v>679.0</v>
+        <v>693.0</v>
       </c>
       <c r="O6" s="2">
-        <v>324.0</v>
+        <v>336.0</v>
       </c>
       <c r="P6" s="2">
-        <v>355.0</v>
+        <v>357.0</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0</v>
@@ -882,7 +882,7 @@
         <v>711.0</v>
       </c>
       <c r="J8" s="2">
-        <v>428.0</v>
+        <v>437.0</v>
       </c>
       <c r="K8" s="2">
         <v>1.0</v>
@@ -894,13 +894,13 @@
         <v>0.0</v>
       </c>
       <c r="N8" s="2">
-        <v>428.0</v>
+        <v>437.0</v>
       </c>
       <c r="O8" s="2">
-        <v>228.0</v>
+        <v>236.0</v>
       </c>
       <c r="P8" s="2">
-        <v>200.0</v>
+        <v>201.0</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0</v>
@@ -1095,7 +1095,7 @@
         <v>561.0</v>
       </c>
       <c r="J11" s="2">
-        <v>372.0</v>
+        <v>390.0</v>
       </c>
       <c r="K11" s="2">
         <v>1.0</v>
@@ -1107,10 +1107,10 @@
         <v>0.0</v>
       </c>
       <c r="N11" s="2">
-        <v>372.0</v>
+        <v>390.0</v>
       </c>
       <c r="O11" s="2">
-        <v>219.0</v>
+        <v>237.0</v>
       </c>
       <c r="P11" s="2">
         <v>153.0</v>
@@ -1308,7 +1308,7 @@
         <v>1342.0</v>
       </c>
       <c r="J14" s="2">
-        <v>793.0</v>
+        <v>863.0</v>
       </c>
       <c r="K14" s="2">
         <v>1.0</v>
@@ -1320,13 +1320,13 @@
         <v>0.0</v>
       </c>
       <c r="N14" s="2">
-        <v>793.0</v>
+        <v>863.0</v>
       </c>
       <c r="O14" s="2">
-        <v>399.0</v>
+        <v>459.0</v>
       </c>
       <c r="P14" s="2">
-        <v>392.0</v>
+        <v>402.0</v>
       </c>
       <c r="Q14" s="2">
         <v>2.0</v>
@@ -1379,7 +1379,7 @@
         <v>791.0</v>
       </c>
       <c r="J15" s="2">
-        <v>487.0</v>
+        <v>518.0</v>
       </c>
       <c r="K15" s="2">
         <v>1.0</v>
@@ -1391,13 +1391,13 @@
         <v>0.0</v>
       </c>
       <c r="N15" s="2">
-        <v>487.0</v>
+        <v>518.0</v>
       </c>
       <c r="O15" s="2">
-        <v>225.0</v>
+        <v>252.0</v>
       </c>
       <c r="P15" s="2">
-        <v>262.0</v>
+        <v>266.0</v>
       </c>
       <c r="Q15" s="2">
         <v>0.0</v>
@@ -1450,7 +1450,7 @@
         <v>692.0</v>
       </c>
       <c r="J16" s="2">
-        <v>526.0</v>
+        <v>530.0</v>
       </c>
       <c r="K16" s="2">
         <v>1.0</v>
@@ -1462,13 +1462,13 @@
         <v>0.0</v>
       </c>
       <c r="N16" s="2">
-        <v>526.0</v>
+        <v>530.0</v>
       </c>
       <c r="O16" s="2">
-        <v>242.0</v>
+        <v>244.0</v>
       </c>
       <c r="P16" s="2">
-        <v>284.0</v>
+        <v>286.0</v>
       </c>
       <c r="Q16" s="2">
         <v>0.0</v>
@@ -1521,7 +1521,7 @@
         <v>829.0</v>
       </c>
       <c r="J17" s="2">
-        <v>546.0</v>
+        <v>582.0</v>
       </c>
       <c r="K17" s="2">
         <v>1.0</v>
@@ -1533,13 +1533,13 @@
         <v>0.0</v>
       </c>
       <c r="N17" s="2">
-        <v>546.0</v>
+        <v>582.0</v>
       </c>
       <c r="O17" s="2">
-        <v>264.0</v>
+        <v>291.0</v>
       </c>
       <c r="P17" s="2">
-        <v>282.0</v>
+        <v>291.0</v>
       </c>
       <c r="Q17" s="2">
         <v>0.0</v>
@@ -1592,7 +1592,7 @@
         <v>1182.0</v>
       </c>
       <c r="J18" s="2">
-        <v>1106.0</v>
+        <v>1111.0</v>
       </c>
       <c r="K18" s="2">
         <v>1.0</v>
@@ -1604,10 +1604,10 @@
         <v>0.0</v>
       </c>
       <c r="N18" s="2">
-        <v>1106.0</v>
+        <v>1111.0</v>
       </c>
       <c r="O18" s="2">
-        <v>579.0</v>
+        <v>584.0</v>
       </c>
       <c r="P18" s="2">
         <v>527.0</v>
@@ -1619,19 +1619,19 @@
         <v>25.0</v>
       </c>
       <c r="S18" s="2">
-        <v>34.0</v>
+        <v>40.0</v>
       </c>
       <c r="T18" s="2">
         <v>2.0</v>
       </c>
       <c r="U18" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="V18" s="2">
         <v>2.0</v>
       </c>
       <c r="W18" s="2">
-        <v>73.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="19">
@@ -1663,7 +1663,7 @@
         <v>940.0</v>
       </c>
       <c r="J19" s="2">
-        <v>693.0</v>
+        <v>697.0</v>
       </c>
       <c r="K19" s="2">
         <v>1.0</v>
@@ -1675,13 +1675,13 @@
         <v>0.0</v>
       </c>
       <c r="N19" s="2">
-        <v>693.0</v>
+        <v>697.0</v>
       </c>
       <c r="O19" s="2">
-        <v>366.0</v>
+        <v>368.0</v>
       </c>
       <c r="P19" s="2">
-        <v>327.0</v>
+        <v>329.0</v>
       </c>
       <c r="Q19" s="2">
         <v>0.0</v>
@@ -1693,7 +1693,7 @@
         <v>19.0</v>
       </c>
       <c r="T19" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="U19" s="2">
         <v>1.0</v>
@@ -1702,7 +1702,7 @@
         <v>0.0</v>
       </c>
       <c r="W19" s="2">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="20">
@@ -1734,7 +1734,7 @@
         <v>1257.0</v>
       </c>
       <c r="J20" s="2">
-        <v>1019.0</v>
+        <v>1042.0</v>
       </c>
       <c r="K20" s="2">
         <v>1.0</v>
@@ -1746,13 +1746,13 @@
         <v>1.0</v>
       </c>
       <c r="N20" s="2">
-        <v>1018.0</v>
+        <v>1041.0</v>
       </c>
       <c r="O20" s="2">
-        <v>581.0</v>
+        <v>599.0</v>
       </c>
       <c r="P20" s="2">
-        <v>438.0</v>
+        <v>443.0</v>
       </c>
       <c r="Q20" s="2">
         <v>0.0</v>
@@ -1805,7 +1805,7 @@
         <v>926.0</v>
       </c>
       <c r="J21" s="2">
-        <v>629.0</v>
+        <v>651.0</v>
       </c>
       <c r="K21" s="2">
         <v>1.0</v>
@@ -1817,13 +1817,13 @@
         <v>0.0</v>
       </c>
       <c r="N21" s="2">
-        <v>629.0</v>
+        <v>651.0</v>
       </c>
       <c r="O21" s="2">
-        <v>322.0</v>
+        <v>336.0</v>
       </c>
       <c r="P21" s="2">
-        <v>307.0</v>
+        <v>315.0</v>
       </c>
       <c r="Q21" s="2">
         <v>0.0</v>
@@ -1971,7 +1971,7 @@
         <v>0.0</v>
       </c>
       <c r="R23" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S23" s="2">
         <v>0.0</v>
@@ -1986,7 +1986,7 @@
         <v>0.0</v>
       </c>
       <c r="W23" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -2018,7 +2018,7 @@
         <v>1296.0</v>
       </c>
       <c r="J24" s="2">
-        <v>742.0</v>
+        <v>750.0</v>
       </c>
       <c r="K24" s="2">
         <v>1.0</v>
@@ -2030,13 +2030,13 @@
         <v>0.0</v>
       </c>
       <c r="N24" s="2">
-        <v>742.0</v>
+        <v>750.0</v>
       </c>
       <c r="O24" s="2">
-        <v>429.0</v>
+        <v>434.0</v>
       </c>
       <c r="P24" s="2">
-        <v>298.0</v>
+        <v>301.0</v>
       </c>
       <c r="Q24" s="2">
         <v>15.0</v>
@@ -2089,7 +2089,7 @@
         <v>372.0</v>
       </c>
       <c r="J25" s="2">
-        <v>303.0</v>
+        <v>304.0</v>
       </c>
       <c r="K25" s="2">
         <v>1.0</v>
@@ -2101,10 +2101,10 @@
         <v>0.0</v>
       </c>
       <c r="N25" s="2">
-        <v>303.0</v>
+        <v>304.0</v>
       </c>
       <c r="O25" s="2">
-        <v>215.0</v>
+        <v>216.0</v>
       </c>
       <c r="P25" s="2">
         <v>88.0</v>
@@ -2302,7 +2302,7 @@
         <v>1349.0</v>
       </c>
       <c r="J28" s="2">
-        <v>982.0</v>
+        <v>1002.0</v>
       </c>
       <c r="K28" s="2">
         <v>1.0</v>
@@ -2314,19 +2314,19 @@
         <v>0.0</v>
       </c>
       <c r="N28" s="2">
-        <v>982.0</v>
+        <v>1002.0</v>
       </c>
       <c r="O28" s="2">
-        <v>530.0</v>
+        <v>545.0</v>
       </c>
       <c r="P28" s="2">
-        <v>450.0</v>
+        <v>455.0</v>
       </c>
       <c r="Q28" s="2">
         <v>2.0</v>
       </c>
       <c r="R28" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S28" s="2">
         <v>2.0</v>
@@ -2341,7 +2341,7 @@
         <v>0.0</v>
       </c>
       <c r="W28" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -2515,7 +2515,7 @@
         <v>1214.0</v>
       </c>
       <c r="J31" s="2">
-        <v>649.0</v>
+        <v>679.0</v>
       </c>
       <c r="K31" s="2">
         <v>1.0</v>
@@ -2527,13 +2527,13 @@
         <v>0.0</v>
       </c>
       <c r="N31" s="2">
-        <v>649.0</v>
+        <v>679.0</v>
       </c>
       <c r="O31" s="2">
-        <v>324.0</v>
+        <v>342.0</v>
       </c>
       <c r="P31" s="2">
-        <v>320.0</v>
+        <v>332.0</v>
       </c>
       <c r="Q31" s="2">
         <v>5.0</v>
@@ -2728,7 +2728,7 @@
         <v>647.0</v>
       </c>
       <c r="J34" s="2">
-        <v>608.0</v>
+        <v>612.0</v>
       </c>
       <c r="K34" s="2">
         <v>1.0</v>
@@ -2740,10 +2740,10 @@
         <v>0.0</v>
       </c>
       <c r="N34" s="2">
-        <v>608.0</v>
+        <v>612.0</v>
       </c>
       <c r="O34" s="2">
-        <v>339.0</v>
+        <v>343.0</v>
       </c>
       <c r="P34" s="2">
         <v>269.0</v>
@@ -2799,7 +2799,7 @@
         <v>554.0</v>
       </c>
       <c r="J35" s="2">
-        <v>378.0</v>
+        <v>400.0</v>
       </c>
       <c r="K35" s="2">
         <v>1.0</v>
@@ -2811,13 +2811,13 @@
         <v>0.0</v>
       </c>
       <c r="N35" s="2">
-        <v>378.0</v>
+        <v>400.0</v>
       </c>
       <c r="O35" s="2">
-        <v>195.0</v>
+        <v>208.0</v>
       </c>
       <c r="P35" s="2">
-        <v>174.0</v>
+        <v>183.0</v>
       </c>
       <c r="Q35" s="2">
         <v>9.0</v>
@@ -2870,7 +2870,7 @@
         <v>1103.0</v>
       </c>
       <c r="J36" s="2">
-        <v>507.0</v>
+        <v>530.0</v>
       </c>
       <c r="K36" s="2">
         <v>1.0</v>
@@ -2882,13 +2882,13 @@
         <v>0.0</v>
       </c>
       <c r="N36" s="2">
-        <v>507.0</v>
+        <v>530.0</v>
       </c>
       <c r="O36" s="2">
-        <v>216.0</v>
+        <v>228.0</v>
       </c>
       <c r="P36" s="2">
-        <v>291.0</v>
+        <v>302.0</v>
       </c>
       <c r="Q36" s="2">
         <v>0.0</v>
@@ -2941,7 +2941,7 @@
         <v>586.0</v>
       </c>
       <c r="J37" s="2">
-        <v>446.0</v>
+        <v>450.0</v>
       </c>
       <c r="K37" s="2">
         <v>1.0</v>
@@ -2953,13 +2953,13 @@
         <v>0.0</v>
       </c>
       <c r="N37" s="2">
-        <v>446.0</v>
+        <v>450.0</v>
       </c>
       <c r="O37" s="2">
-        <v>230.0</v>
+        <v>233.0</v>
       </c>
       <c r="P37" s="2">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
       <c r="Q37" s="2">
         <v>4.0</v>
@@ -3012,7 +3012,7 @@
         <v>1123.0</v>
       </c>
       <c r="J38" s="2">
-        <v>929.0</v>
+        <v>945.0</v>
       </c>
       <c r="K38" s="2">
         <v>1.0</v>
@@ -3024,13 +3024,13 @@
         <v>0.0</v>
       </c>
       <c r="N38" s="2">
-        <v>929.0</v>
+        <v>945.0</v>
       </c>
       <c r="O38" s="2">
-        <v>542.0</v>
+        <v>553.0</v>
       </c>
       <c r="P38" s="2">
-        <v>387.0</v>
+        <v>392.0</v>
       </c>
       <c r="Q38" s="2">
         <v>0.0</v>
@@ -3225,7 +3225,7 @@
         <v>1244.0</v>
       </c>
       <c r="J41" s="2">
-        <v>912.0</v>
+        <v>918.0</v>
       </c>
       <c r="K41" s="2">
         <v>1.0</v>
@@ -3237,13 +3237,13 @@
         <v>0.0</v>
       </c>
       <c r="N41" s="2">
-        <v>912.0</v>
+        <v>918.0</v>
       </c>
       <c r="O41" s="2">
         <v>432.0</v>
       </c>
       <c r="P41" s="2">
-        <v>480.0</v>
+        <v>486.0</v>
       </c>
       <c r="Q41" s="2">
         <v>0.0</v>
@@ -3296,7 +3296,7 @@
         <v>1005.0</v>
       </c>
       <c r="J42" s="2">
-        <v>490.0</v>
+        <v>524.0</v>
       </c>
       <c r="K42" s="2">
         <v>1.0</v>
@@ -3308,13 +3308,13 @@
         <v>0.0</v>
       </c>
       <c r="N42" s="2">
-        <v>490.0</v>
+        <v>524.0</v>
       </c>
       <c r="O42" s="2">
-        <v>317.0</v>
+        <v>341.0</v>
       </c>
       <c r="P42" s="2">
-        <v>173.0</v>
+        <v>183.0</v>
       </c>
       <c r="Q42" s="2">
         <v>0.0</v>
@@ -3367,7 +3367,7 @@
         <v>1022.0</v>
       </c>
       <c r="J43" s="2">
-        <v>717.0</v>
+        <v>767.0</v>
       </c>
       <c r="K43" s="2">
         <v>1.0</v>
@@ -3379,16 +3379,16 @@
         <v>0.0</v>
       </c>
       <c r="N43" s="2">
-        <v>717.0</v>
+        <v>767.0</v>
       </c>
       <c r="O43" s="2">
-        <v>348.0</v>
+        <v>387.0</v>
       </c>
       <c r="P43" s="2">
-        <v>369.0</v>
+        <v>379.0</v>
       </c>
       <c r="Q43" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R43" s="2">
         <v>0.0</v>
@@ -3438,7 +3438,7 @@
         <v>1094.0</v>
       </c>
       <c r="J44" s="2">
-        <v>951.0</v>
+        <v>956.0</v>
       </c>
       <c r="K44" s="2">
         <v>1.0</v>
@@ -3450,10 +3450,10 @@
         <v>0.0</v>
       </c>
       <c r="N44" s="2">
-        <v>951.0</v>
+        <v>956.0</v>
       </c>
       <c r="O44" s="2">
-        <v>484.0</v>
+        <v>489.0</v>
       </c>
       <c r="P44" s="2">
         <v>466.0</v>
@@ -3675,7 +3675,7 @@
         <v>1.0</v>
       </c>
       <c r="R47" s="2">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="S47" s="2">
         <v>0.0</v>
@@ -3690,7 +3690,7 @@
         <v>0.0</v>
       </c>
       <c r="W47" s="2">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
@@ -3722,7 +3722,7 @@
         <v>1102.0</v>
       </c>
       <c r="J48" s="2">
-        <v>901.0</v>
+        <v>902.0</v>
       </c>
       <c r="K48" s="2">
         <v>1.0</v>
@@ -3734,10 +3734,10 @@
         <v>0.0</v>
       </c>
       <c r="N48" s="2">
-        <v>901.0</v>
+        <v>902.0</v>
       </c>
       <c r="O48" s="2">
-        <v>517.0</v>
+        <v>518.0</v>
       </c>
       <c r="P48" s="2">
         <v>384.0</v>
@@ -3793,7 +3793,7 @@
         <v>1437.0</v>
       </c>
       <c r="J49" s="2">
-        <v>939.0</v>
+        <v>957.0</v>
       </c>
       <c r="K49" s="2">
         <v>1.0</v>
@@ -3805,16 +3805,16 @@
         <v>0.0</v>
       </c>
       <c r="N49" s="2">
-        <v>939.0</v>
+        <v>957.0</v>
       </c>
       <c r="O49" s="2">
-        <v>501.0</v>
+        <v>509.0</v>
       </c>
       <c r="P49" s="2">
         <v>438.0</v>
       </c>
       <c r="Q49" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="R49" s="2">
         <v>34.0</v>
@@ -4006,7 +4006,7 @@
         <v>605.0</v>
       </c>
       <c r="J52" s="2">
-        <v>506.0</v>
+        <v>537.0</v>
       </c>
       <c r="K52" s="2">
         <v>1.0</v>
@@ -4018,13 +4018,13 @@
         <v>0.0</v>
       </c>
       <c r="N52" s="2">
-        <v>506.0</v>
+        <v>537.0</v>
       </c>
       <c r="O52" s="2">
-        <v>233.0</v>
+        <v>261.0</v>
       </c>
       <c r="P52" s="2">
-        <v>273.0</v>
+        <v>276.0</v>
       </c>
       <c r="Q52" s="2">
         <v>0.0</v>
@@ -4077,7 +4077,7 @@
         <v>834.0</v>
       </c>
       <c r="J53" s="2">
-        <v>776.0</v>
+        <v>810.0</v>
       </c>
       <c r="K53" s="2">
         <v>1.0</v>
@@ -4089,25 +4089,25 @@
         <v>0.0</v>
       </c>
       <c r="N53" s="2">
-        <v>776.0</v>
+        <v>810.0</v>
       </c>
       <c r="O53" s="2">
-        <v>433.0</v>
+        <v>447.0</v>
       </c>
       <c r="P53" s="2">
-        <v>343.0</v>
+        <v>358.0</v>
       </c>
       <c r="Q53" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="R53" s="2">
         <v>5.0</v>
       </c>
       <c r="S53" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T53" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="U53" s="2">
         <v>0.0</v>
@@ -4116,7 +4116,7 @@
         <v>0.0</v>
       </c>
       <c r="W53" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
@@ -4148,7 +4148,7 @@
         <v>778.0</v>
       </c>
       <c r="J54" s="2">
-        <v>590.0</v>
+        <v>606.0</v>
       </c>
       <c r="K54" s="2">
         <v>1.0</v>
@@ -4160,16 +4160,16 @@
         <v>0.0</v>
       </c>
       <c r="N54" s="2">
-        <v>590.0</v>
+        <v>606.0</v>
       </c>
       <c r="O54" s="2">
-        <v>311.0</v>
+        <v>318.0</v>
       </c>
       <c r="P54" s="2">
-        <v>279.0</v>
+        <v>283.0</v>
       </c>
       <c r="Q54" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="R54" s="2">
         <v>0.0</v>
@@ -4219,7 +4219,7 @@
         <v>540.0</v>
       </c>
       <c r="J55" s="2">
-        <v>350.0</v>
+        <v>391.0</v>
       </c>
       <c r="K55" s="2">
         <v>1.0</v>
@@ -4231,13 +4231,13 @@
         <v>0.0</v>
       </c>
       <c r="N55" s="2">
-        <v>350.0</v>
+        <v>391.0</v>
       </c>
       <c r="O55" s="2">
-        <v>149.0</v>
+        <v>168.0</v>
       </c>
       <c r="P55" s="2">
-        <v>201.0</v>
+        <v>223.0</v>
       </c>
       <c r="Q55" s="2">
         <v>0.0</v>
@@ -4290,7 +4290,7 @@
         <v>615.0</v>
       </c>
       <c r="J56" s="2">
-        <v>554.0</v>
+        <v>568.0</v>
       </c>
       <c r="K56" s="2">
         <v>1.0</v>
@@ -4302,10 +4302,10 @@
         <v>0.0</v>
       </c>
       <c r="N56" s="2">
-        <v>554.0</v>
+        <v>568.0</v>
       </c>
       <c r="O56" s="2">
-        <v>268.0</v>
+        <v>282.0</v>
       </c>
       <c r="P56" s="2">
         <v>286.0</v>
@@ -4361,7 +4361,7 @@
         <v>620.0</v>
       </c>
       <c r="J57" s="2">
-        <v>507.0</v>
+        <v>528.0</v>
       </c>
       <c r="K57" s="2">
         <v>1.0</v>
@@ -4373,10 +4373,10 @@
         <v>0.0</v>
       </c>
       <c r="N57" s="2">
-        <v>507.0</v>
+        <v>528.0</v>
       </c>
       <c r="O57" s="2">
-        <v>507.0</v>
+        <v>528.0</v>
       </c>
       <c r="P57" s="2">
         <v>0.0</v>
@@ -4432,7 +4432,7 @@
         <v>1059.0</v>
       </c>
       <c r="J58" s="2">
-        <v>739.0</v>
+        <v>833.0</v>
       </c>
       <c r="K58" s="2">
         <v>1.0</v>
@@ -4444,13 +4444,13 @@
         <v>0.0</v>
       </c>
       <c r="N58" s="2">
-        <v>739.0</v>
+        <v>833.0</v>
       </c>
       <c r="O58" s="2">
-        <v>367.0</v>
+        <v>442.0</v>
       </c>
       <c r="P58" s="2">
-        <v>372.0</v>
+        <v>391.0</v>
       </c>
       <c r="Q58" s="2">
         <v>0.0</v>
@@ -4503,7 +4503,7 @@
         <v>909.0</v>
       </c>
       <c r="J59" s="2">
-        <v>652.0</v>
+        <v>672.0</v>
       </c>
       <c r="K59" s="2">
         <v>1.0</v>
@@ -4515,19 +4515,19 @@
         <v>0.0</v>
       </c>
       <c r="N59" s="2">
-        <v>652.0</v>
+        <v>672.0</v>
       </c>
       <c r="O59" s="2">
-        <v>314.0</v>
+        <v>324.0</v>
       </c>
       <c r="P59" s="2">
-        <v>338.0</v>
+        <v>348.0</v>
       </c>
       <c r="Q59" s="2">
         <v>0.0</v>
       </c>
       <c r="R59" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S59" s="2">
         <v>1.0</v>
@@ -4542,7 +4542,7 @@
         <v>0.0</v>
       </c>
       <c r="W59" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
@@ -4574,7 +4574,7 @@
         <v>707.0</v>
       </c>
       <c r="J60" s="2">
-        <v>601.0</v>
+        <v>607.0</v>
       </c>
       <c r="K60" s="2">
         <v>1.0</v>
@@ -4586,34 +4586,34 @@
         <v>0.0</v>
       </c>
       <c r="N60" s="2">
-        <v>601.0</v>
+        <v>607.0</v>
       </c>
       <c r="O60" s="2">
-        <v>267.0</v>
+        <v>268.0</v>
       </c>
       <c r="P60" s="2">
-        <v>334.0</v>
+        <v>339.0</v>
       </c>
       <c r="Q60" s="2">
         <v>0.0</v>
       </c>
       <c r="R60" s="2">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="S60" s="2">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="T60" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="U60" s="2">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="V60" s="2">
         <v>0.0</v>
       </c>
       <c r="W60" s="2">
-        <v>1.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
@@ -4716,7 +4716,7 @@
         <v>570.0</v>
       </c>
       <c r="J62" s="2">
-        <v>506.0</v>
+        <v>508.0</v>
       </c>
       <c r="K62" s="2">
         <v>1.0</v>
@@ -4728,10 +4728,10 @@
         <v>0.0</v>
       </c>
       <c r="N62" s="2">
-        <v>506.0</v>
+        <v>508.0</v>
       </c>
       <c r="O62" s="2">
-        <v>274.0</v>
+        <v>276.0</v>
       </c>
       <c r="P62" s="2">
         <v>231.0</v>
@@ -4743,19 +4743,19 @@
         <v>32.0</v>
       </c>
       <c r="S62" s="2">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="T62" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U62" s="2">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="V62" s="2">
         <v>0.0</v>
       </c>
       <c r="W62" s="2">
-        <v>32.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
@@ -4858,7 +4858,7 @@
         <v>1113.0</v>
       </c>
       <c r="J64" s="2">
-        <v>1041.0</v>
+        <v>1042.0</v>
       </c>
       <c r="K64" s="2">
         <v>1.0</v>
@@ -4870,10 +4870,10 @@
         <v>0.0</v>
       </c>
       <c r="N64" s="2">
-        <v>1041.0</v>
+        <v>1042.0</v>
       </c>
       <c r="O64" s="2">
-        <v>587.0</v>
+        <v>588.0</v>
       </c>
       <c r="P64" s="2">
         <v>454.0</v>
@@ -5000,7 +5000,7 @@
         <v>1155.0</v>
       </c>
       <c r="J66" s="2">
-        <v>1037.0</v>
+        <v>1039.0</v>
       </c>
       <c r="K66" s="2">
         <v>1.0</v>
@@ -5012,25 +5012,25 @@
         <v>0.0</v>
       </c>
       <c r="N66" s="2">
-        <v>1037.0</v>
+        <v>1039.0</v>
       </c>
       <c r="O66" s="2">
-        <v>563.0</v>
+        <v>564.0</v>
       </c>
       <c r="P66" s="2">
-        <v>472.0</v>
+        <v>473.0</v>
       </c>
       <c r="Q66" s="2">
         <v>2.0</v>
       </c>
       <c r="R66" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="S66" s="2">
-        <v>41.0</v>
+        <v>51.0</v>
       </c>
       <c r="T66" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U66" s="2">
         <v>0.0</v>
@@ -5039,7 +5039,7 @@
         <v>0.0</v>
       </c>
       <c r="W66" s="2">
-        <v>54.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
@@ -5071,7 +5071,7 @@
         <v>1129.0</v>
       </c>
       <c r="J67" s="2">
-        <v>912.0</v>
+        <v>925.0</v>
       </c>
       <c r="K67" s="2">
         <v>1.0</v>
@@ -5083,13 +5083,13 @@
         <v>0.0</v>
       </c>
       <c r="N67" s="2">
-        <v>912.0</v>
+        <v>925.0</v>
       </c>
       <c r="O67" s="2">
-        <v>412.0</v>
+        <v>422.0</v>
       </c>
       <c r="P67" s="2">
-        <v>499.0</v>
+        <v>502.0</v>
       </c>
       <c r="Q67" s="2">
         <v>1.0</v>
@@ -5142,7 +5142,7 @@
         <v>1042.0</v>
       </c>
       <c r="J68" s="2">
-        <v>968.0</v>
+        <v>983.0</v>
       </c>
       <c r="K68" s="2">
         <v>1.0</v>
@@ -5154,7 +5154,7 @@
         <v>0.0</v>
       </c>
       <c r="N68" s="2">
-        <v>968.0</v>
+        <v>983.0</v>
       </c>
       <c r="O68" s="2">
         <v>529.0</v>
@@ -5163,13 +5163,13 @@
         <v>439.0</v>
       </c>
       <c r="Q68" s="2">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="R68" s="2">
         <v>0.0</v>
       </c>
       <c r="S68" s="2">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="T68" s="2">
         <v>0.0</v>
@@ -5181,7 +5181,7 @@
         <v>0.0</v>
       </c>
       <c r="W68" s="2">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
@@ -5213,7 +5213,7 @@
         <v>1122.0</v>
       </c>
       <c r="J69" s="2">
-        <v>973.0</v>
+        <v>983.0</v>
       </c>
       <c r="K69" s="2">
         <v>1.0</v>
@@ -5225,13 +5225,13 @@
         <v>1.0</v>
       </c>
       <c r="N69" s="2">
-        <v>972.0</v>
+        <v>982.0</v>
       </c>
       <c r="O69" s="2">
-        <v>500.0</v>
+        <v>508.0</v>
       </c>
       <c r="P69" s="2">
-        <v>473.0</v>
+        <v>475.0</v>
       </c>
       <c r="Q69" s="2">
         <v>0.0</v>
@@ -5284,7 +5284,7 @@
         <v>1151.0</v>
       </c>
       <c r="J70" s="2">
-        <v>1021.0</v>
+        <v>1061.0</v>
       </c>
       <c r="K70" s="2">
         <v>1.0</v>
@@ -5296,19 +5296,19 @@
         <v>0.0</v>
       </c>
       <c r="N70" s="2">
-        <v>1021.0</v>
+        <v>1061.0</v>
       </c>
       <c r="O70" s="2">
-        <v>638.0</v>
+        <v>658.0</v>
       </c>
       <c r="P70" s="2">
-        <v>374.0</v>
+        <v>393.0</v>
       </c>
       <c r="Q70" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="R70" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="S70" s="2">
         <v>1.0</v>
@@ -5323,7 +5323,7 @@
         <v>0.0</v>
       </c>
       <c r="W70" s="2">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
@@ -5426,7 +5426,7 @@
         <v>1141.0</v>
       </c>
       <c r="J72" s="2">
-        <v>1060.0</v>
+        <v>1065.0</v>
       </c>
       <c r="K72" s="2">
         <v>1.0</v>
@@ -5438,13 +5438,13 @@
         <v>0.0</v>
       </c>
       <c r="N72" s="2">
-        <v>1060.0</v>
+        <v>1065.0</v>
       </c>
       <c r="O72" s="2">
-        <v>657.0</v>
+        <v>660.0</v>
       </c>
       <c r="P72" s="2">
-        <v>395.0</v>
+        <v>397.0</v>
       </c>
       <c r="Q72" s="2">
         <v>8.0</v>
@@ -5456,16 +5456,16 @@
         <v>11.0</v>
       </c>
       <c r="T72" s="2">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="U72" s="2">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="V72" s="2">
         <v>0.0</v>
       </c>
       <c r="W72" s="2">
-        <v>75.0</v>
+        <v>77.0</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
@@ -5497,7 +5497,7 @@
         <v>973.0</v>
       </c>
       <c r="J73" s="2">
-        <v>909.0</v>
+        <v>922.0</v>
       </c>
       <c r="K73" s="2">
         <v>1.0</v>
@@ -5509,10 +5509,10 @@
         <v>0.0</v>
       </c>
       <c r="N73" s="2">
-        <v>909.0</v>
+        <v>922.0</v>
       </c>
       <c r="O73" s="2">
-        <v>459.0</v>
+        <v>472.0</v>
       </c>
       <c r="P73" s="2">
         <v>443.0</v>
@@ -5639,7 +5639,7 @@
         <v>877.0</v>
       </c>
       <c r="J75" s="2">
-        <v>811.0</v>
+        <v>812.0</v>
       </c>
       <c r="K75" s="2">
         <v>1.0</v>
@@ -5651,10 +5651,10 @@
         <v>0.0</v>
       </c>
       <c r="N75" s="2">
-        <v>811.0</v>
+        <v>812.0</v>
       </c>
       <c r="O75" s="2">
-        <v>424.0</v>
+        <v>425.0</v>
       </c>
       <c r="P75" s="2">
         <v>377.0</v>
@@ -5710,7 +5710,7 @@
         <v>970.0</v>
       </c>
       <c r="J76" s="2">
-        <v>778.0</v>
+        <v>803.0</v>
       </c>
       <c r="K76" s="2">
         <v>1.0</v>
@@ -5722,13 +5722,13 @@
         <v>0.0</v>
       </c>
       <c r="N76" s="2">
-        <v>778.0</v>
+        <v>803.0</v>
       </c>
       <c r="O76" s="2">
-        <v>419.0</v>
+        <v>434.0</v>
       </c>
       <c r="P76" s="2">
-        <v>359.0</v>
+        <v>369.0</v>
       </c>
       <c r="Q76" s="2">
         <v>0.0</v>
@@ -5781,7 +5781,7 @@
         <v>792.0</v>
       </c>
       <c r="J77" s="2">
-        <v>429.0</v>
+        <v>504.0</v>
       </c>
       <c r="K77" s="2">
         <v>1.0</v>
@@ -5793,7 +5793,7 @@
         <v>0.0</v>
       </c>
       <c r="N77" s="2">
-        <v>429.0</v>
+        <v>504.0</v>
       </c>
       <c r="O77" s="2">
         <v>58.0</v>
@@ -5802,7 +5802,7 @@
         <v>303.0</v>
       </c>
       <c r="Q77" s="2">
-        <v>68.0</v>
+        <v>143.0</v>
       </c>
       <c r="R77" s="2">
         <v>0.0</v>
@@ -5852,7 +5852,7 @@
         <v>1275.0</v>
       </c>
       <c r="J78" s="2">
-        <v>465.0</v>
+        <v>514.0</v>
       </c>
       <c r="K78" s="2">
         <v>1.0</v>
@@ -5864,13 +5864,13 @@
         <v>0.0</v>
       </c>
       <c r="N78" s="2">
-        <v>465.0</v>
+        <v>514.0</v>
       </c>
       <c r="O78" s="2">
-        <v>165.0</v>
+        <v>166.0</v>
       </c>
       <c r="P78" s="2">
-        <v>300.0</v>
+        <v>348.0</v>
       </c>
       <c r="Q78" s="2">
         <v>0.0</v>
@@ -5994,7 +5994,7 @@
         <v>1333.0</v>
       </c>
       <c r="J80" s="2">
-        <v>833.0</v>
+        <v>841.0</v>
       </c>
       <c r="K80" s="2">
         <v>1.0</v>
@@ -6006,13 +6006,13 @@
         <v>0.0</v>
       </c>
       <c r="N80" s="2">
-        <v>833.0</v>
+        <v>841.0</v>
       </c>
       <c r="O80" s="2">
-        <v>455.0</v>
+        <v>461.0</v>
       </c>
       <c r="P80" s="2">
-        <v>378.0</v>
+        <v>380.0</v>
       </c>
       <c r="Q80" s="2">
         <v>0.0</v>
@@ -6065,7 +6065,7 @@
         <v>796.0</v>
       </c>
       <c r="J81" s="2">
-        <v>679.0</v>
+        <v>700.0</v>
       </c>
       <c r="K81" s="2">
         <v>1.0</v>
@@ -6077,13 +6077,13 @@
         <v>0.0</v>
       </c>
       <c r="N81" s="2">
-        <v>679.0</v>
+        <v>700.0</v>
       </c>
       <c r="O81" s="2">
-        <v>354.0</v>
+        <v>366.0</v>
       </c>
       <c r="P81" s="2">
-        <v>325.0</v>
+        <v>334.0</v>
       </c>
       <c r="Q81" s="2">
         <v>0.0</v>
@@ -6092,7 +6092,7 @@
         <v>18.0</v>
       </c>
       <c r="S81" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="T81" s="2">
         <v>4.0</v>
@@ -6104,7 +6104,7 @@
         <v>0.0</v>
       </c>
       <c r="W81" s="2">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
@@ -6136,7 +6136,7 @@
         <v>1157.0</v>
       </c>
       <c r="J82" s="2">
-        <v>826.0</v>
+        <v>841.0</v>
       </c>
       <c r="K82" s="2">
         <v>1.0</v>
@@ -6148,19 +6148,19 @@
         <v>0.0</v>
       </c>
       <c r="N82" s="2">
-        <v>826.0</v>
+        <v>841.0</v>
       </c>
       <c r="O82" s="2">
-        <v>392.0</v>
+        <v>397.0</v>
       </c>
       <c r="P82" s="2">
-        <v>434.0</v>
+        <v>444.0</v>
       </c>
       <c r="Q82" s="2">
         <v>0.0</v>
       </c>
       <c r="R82" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S82" s="2">
         <v>0.0</v>
@@ -6175,7 +6175,7 @@
         <v>0.0</v>
       </c>
       <c r="W82" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
@@ -6278,7 +6278,7 @@
         <v>451.0</v>
       </c>
       <c r="J84" s="2">
-        <v>376.0</v>
+        <v>380.0</v>
       </c>
       <c r="K84" s="2">
         <v>1.0</v>
@@ -6290,13 +6290,13 @@
         <v>0.0</v>
       </c>
       <c r="N84" s="2">
-        <v>376.0</v>
+        <v>380.0</v>
       </c>
       <c r="O84" s="2">
-        <v>175.0</v>
+        <v>178.0</v>
       </c>
       <c r="P84" s="2">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
       <c r="Q84" s="2">
         <v>0.0</v>
@@ -6349,7 +6349,7 @@
         <v>1308.0</v>
       </c>
       <c r="J85" s="2">
-        <v>1076.0</v>
+        <v>1077.0</v>
       </c>
       <c r="K85" s="2">
         <v>1.0</v>
@@ -6361,34 +6361,34 @@
         <v>0.0</v>
       </c>
       <c r="N85" s="2">
-        <v>1076.0</v>
+        <v>1077.0</v>
       </c>
       <c r="O85" s="2">
         <v>519.0</v>
       </c>
       <c r="P85" s="2">
-        <v>557.0</v>
+        <v>558.0</v>
       </c>
       <c r="Q85" s="2">
         <v>0.0</v>
       </c>
       <c r="R85" s="2">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
       <c r="S85" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="T85" s="2">
         <v>0.0</v>
       </c>
       <c r="U85" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V85" s="2">
         <v>0.0</v>
       </c>
       <c r="W85" s="2">
-        <v>0.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
@@ -6562,7 +6562,7 @@
         <v>882.0</v>
       </c>
       <c r="J88" s="2">
-        <v>606.0</v>
+        <v>609.0</v>
       </c>
       <c r="K88" s="2">
         <v>1.0</v>
@@ -6574,13 +6574,13 @@
         <v>0.0</v>
       </c>
       <c r="N88" s="2">
-        <v>606.0</v>
+        <v>609.0</v>
       </c>
       <c r="O88" s="2">
-        <v>281.0</v>
+        <v>282.0</v>
       </c>
       <c r="P88" s="2">
-        <v>325.0</v>
+        <v>327.0</v>
       </c>
       <c r="Q88" s="2">
         <v>0.0</v>
@@ -6633,7 +6633,7 @@
         <v>814.0</v>
       </c>
       <c r="J89" s="2">
-        <v>474.0</v>
+        <v>475.0</v>
       </c>
       <c r="K89" s="2">
         <v>1.0</v>
@@ -6645,10 +6645,10 @@
         <v>0.0</v>
       </c>
       <c r="N89" s="2">
-        <v>474.0</v>
+        <v>475.0</v>
       </c>
       <c r="O89" s="2">
-        <v>207.0</v>
+        <v>208.0</v>
       </c>
       <c r="P89" s="2">
         <v>267.0</v>
@@ -6775,7 +6775,7 @@
         <v>940.0</v>
       </c>
       <c r="J91" s="2">
-        <v>645.0</v>
+        <v>651.0</v>
       </c>
       <c r="K91" s="2">
         <v>1.0</v>
@@ -6787,34 +6787,34 @@
         <v>0.0</v>
       </c>
       <c r="N91" s="2">
-        <v>645.0</v>
+        <v>651.0</v>
       </c>
       <c r="O91" s="2">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="P91" s="2">
-        <v>317.0</v>
+        <v>319.0</v>
       </c>
       <c r="Q91" s="2">
-        <v>200.0</v>
+        <v>203.0</v>
       </c>
       <c r="R91" s="2">
         <v>43.0</v>
       </c>
       <c r="S91" s="2">
-        <v>23.0</v>
+        <v>33.0</v>
       </c>
       <c r="T91" s="2">
         <v>1.0</v>
       </c>
       <c r="U91" s="2">
-        <v>57.0</v>
+        <v>109.0</v>
       </c>
       <c r="V91" s="2">
         <v>1.0</v>
       </c>
       <c r="W91" s="2">
-        <v>125.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
@@ -6917,7 +6917,7 @@
         <v>960.0</v>
       </c>
       <c r="J93" s="2">
-        <v>741.0</v>
+        <v>768.0</v>
       </c>
       <c r="K93" s="2">
         <v>1.0</v>
@@ -6929,13 +6929,13 @@
         <v>0.0</v>
       </c>
       <c r="N93" s="2">
-        <v>741.0</v>
+        <v>768.0</v>
       </c>
       <c r="O93" s="2">
-        <v>415.0</v>
+        <v>437.0</v>
       </c>
       <c r="P93" s="2">
-        <v>325.0</v>
+        <v>330.0</v>
       </c>
       <c r="Q93" s="2">
         <v>1.0</v>
@@ -7059,7 +7059,7 @@
         <v>1421.0</v>
       </c>
       <c r="J95" s="2">
-        <v>1308.0</v>
+        <v>1318.0</v>
       </c>
       <c r="K95" s="2">
         <v>1.0</v>
@@ -7071,13 +7071,13 @@
         <v>0.0</v>
       </c>
       <c r="N95" s="2">
-        <v>1308.0</v>
+        <v>1318.0</v>
       </c>
       <c r="O95" s="2">
-        <v>662.0</v>
+        <v>671.0</v>
       </c>
       <c r="P95" s="2">
-        <v>646.0</v>
+        <v>647.0</v>
       </c>
       <c r="Q95" s="2">
         <v>0.0</v>
@@ -7130,7 +7130,7 @@
         <v>1426.0</v>
       </c>
       <c r="J96" s="2">
-        <v>756.0</v>
+        <v>787.0</v>
       </c>
       <c r="K96" s="2">
         <v>1.0</v>
@@ -7142,13 +7142,13 @@
         <v>0.0</v>
       </c>
       <c r="N96" s="2">
-        <v>756.0</v>
+        <v>787.0</v>
       </c>
       <c r="O96" s="2">
-        <v>401.0</v>
+        <v>423.0</v>
       </c>
       <c r="P96" s="2">
-        <v>355.0</v>
+        <v>364.0</v>
       </c>
       <c r="Q96" s="2">
         <v>0.0</v>
@@ -7272,7 +7272,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" s="2">
-        <v>427.0</v>
+        <v>431.0</v>
       </c>
       <c r="K98" s="2">
         <v>1.0</v>
@@ -7284,22 +7284,22 @@
         <v>0.0</v>
       </c>
       <c r="N98" s="2">
-        <v>427.0</v>
+        <v>431.0</v>
       </c>
       <c r="O98" s="2">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="P98" s="2">
-        <v>253.0</v>
+        <v>255.0</v>
       </c>
       <c r="Q98" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="R98" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="S98" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T98" s="2">
         <v>0.0</v>
@@ -7311,7 +7311,7 @@
         <v>0.0</v>
       </c>
       <c r="W98" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
@@ -7343,7 +7343,7 @@
         <v>878.0</v>
       </c>
       <c r="J99" s="2">
-        <v>709.0</v>
+        <v>717.0</v>
       </c>
       <c r="K99" s="2">
         <v>1.0</v>
@@ -7355,13 +7355,13 @@
         <v>0.0</v>
       </c>
       <c r="N99" s="2">
-        <v>709.0</v>
+        <v>717.0</v>
       </c>
       <c r="O99" s="2">
-        <v>359.0</v>
+        <v>365.0</v>
       </c>
       <c r="P99" s="2">
-        <v>350.0</v>
+        <v>352.0</v>
       </c>
       <c r="Q99" s="2">
         <v>0.0</v>
@@ -7414,7 +7414,7 @@
         <v>1254.0</v>
       </c>
       <c r="J100" s="2">
-        <v>947.0</v>
+        <v>1012.0</v>
       </c>
       <c r="K100" s="2">
         <v>1.0</v>
@@ -7426,13 +7426,13 @@
         <v>0.0</v>
       </c>
       <c r="N100" s="2">
-        <v>947.0</v>
+        <v>1012.0</v>
       </c>
       <c r="O100" s="2">
-        <v>401.0</v>
+        <v>415.0</v>
       </c>
       <c r="P100" s="2">
-        <v>546.0</v>
+        <v>597.0</v>
       </c>
       <c r="Q100" s="2">
         <v>0.0</v>
@@ -7485,7 +7485,7 @@
         <v>1059.0</v>
       </c>
       <c r="J101" s="2">
-        <v>929.0</v>
+        <v>932.0</v>
       </c>
       <c r="K101" s="2">
         <v>1.0</v>
@@ -7497,10 +7497,10 @@
         <v>0.0</v>
       </c>
       <c r="N101" s="2">
-        <v>929.0</v>
+        <v>932.0</v>
       </c>
       <c r="O101" s="2">
-        <v>484.0</v>
+        <v>487.0</v>
       </c>
       <c r="P101" s="2">
         <v>445.0</v>
@@ -7512,7 +7512,7 @@
         <v>46.0</v>
       </c>
       <c r="S101" s="2">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="T101" s="2">
         <v>2.0</v>
@@ -7524,7 +7524,7 @@
         <v>0.0</v>
       </c>
       <c r="W101" s="2">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
@@ -7556,7 +7556,7 @@
         <v>1159.0</v>
       </c>
       <c r="J102" s="2">
-        <v>846.0</v>
+        <v>852.0</v>
       </c>
       <c r="K102" s="2">
         <v>1.0</v>
@@ -7568,22 +7568,22 @@
         <v>0.0</v>
       </c>
       <c r="N102" s="2">
-        <v>846.0</v>
+        <v>852.0</v>
       </c>
       <c r="O102" s="2">
-        <v>420.0</v>
+        <v>425.0</v>
       </c>
       <c r="P102" s="2">
-        <v>426.0</v>
+        <v>427.0</v>
       </c>
       <c r="Q102" s="2">
         <v>0.0</v>
       </c>
       <c r="R102" s="2">
-        <v>36.0</v>
+        <v>50.0</v>
       </c>
       <c r="S102" s="2">
-        <v>26.0</v>
+        <v>51.0</v>
       </c>
       <c r="T102" s="2">
         <v>0.0</v>
@@ -7595,7 +7595,7 @@
         <v>0.0</v>
       </c>
       <c r="W102" s="2">
-        <v>62.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
@@ -7627,7 +7627,7 @@
         <v>663.0</v>
       </c>
       <c r="J103" s="2">
-        <v>440.0</v>
+        <v>451.0</v>
       </c>
       <c r="K103" s="2">
         <v>1.0</v>
@@ -7639,13 +7639,13 @@
         <v>0.0</v>
       </c>
       <c r="N103" s="2">
-        <v>440.0</v>
+        <v>451.0</v>
       </c>
       <c r="O103" s="2">
-        <v>229.0</v>
+        <v>239.0</v>
       </c>
       <c r="P103" s="2">
-        <v>211.0</v>
+        <v>212.0</v>
       </c>
       <c r="Q103" s="2">
         <v>0.0</v>
@@ -7769,7 +7769,7 @@
         <v>1066.0</v>
       </c>
       <c r="J105" s="2">
-        <v>730.0</v>
+        <v>758.0</v>
       </c>
       <c r="K105" s="2">
         <v>1.0</v>
@@ -7781,13 +7781,13 @@
         <v>0.0</v>
       </c>
       <c r="N105" s="2">
-        <v>730.0</v>
+        <v>758.0</v>
       </c>
       <c r="O105" s="2">
-        <v>370.0</v>
+        <v>397.0</v>
       </c>
       <c r="P105" s="2">
-        <v>360.0</v>
+        <v>361.0</v>
       </c>
       <c r="Q105" s="2">
         <v>0.0</v>
@@ -7796,7 +7796,7 @@
         <v>34.0</v>
       </c>
       <c r="S105" s="2">
-        <v>77.0</v>
+        <v>79.0</v>
       </c>
       <c r="T105" s="2">
         <v>0.0</v>
@@ -7808,7 +7808,7 @@
         <v>0.0</v>
       </c>
       <c r="W105" s="2">
-        <v>111.0</v>
+        <v>113.0</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
@@ -7867,7 +7867,7 @@
         <v>31.0</v>
       </c>
       <c r="S106" s="2">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="T106" s="2">
         <v>5.0</v>
@@ -7879,7 +7879,7 @@
         <v>0.0</v>
       </c>
       <c r="W106" s="2">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
@@ -7911,7 +7911,7 @@
         <v>1053.0</v>
       </c>
       <c r="J107" s="2">
-        <v>525.0</v>
+        <v>578.0</v>
       </c>
       <c r="K107" s="2">
         <v>1.0</v>
@@ -7923,13 +7923,13 @@
         <v>3.0</v>
       </c>
       <c r="N107" s="2">
-        <v>522.0</v>
+        <v>575.0</v>
       </c>
       <c r="O107" s="2">
-        <v>260.0</v>
+        <v>291.0</v>
       </c>
       <c r="P107" s="2">
-        <v>265.0</v>
+        <v>287.0</v>
       </c>
       <c r="Q107" s="2">
         <v>0.0</v>
@@ -8053,7 +8053,7 @@
         <v>821.0</v>
       </c>
       <c r="J109" s="2">
-        <v>593.0</v>
+        <v>604.0</v>
       </c>
       <c r="K109" s="2">
         <v>1.0</v>
@@ -8065,13 +8065,13 @@
         <v>0.0</v>
       </c>
       <c r="N109" s="2">
-        <v>593.0</v>
+        <v>604.0</v>
       </c>
       <c r="O109" s="2">
-        <v>313.0</v>
+        <v>317.0</v>
       </c>
       <c r="P109" s="2">
-        <v>280.0</v>
+        <v>287.0</v>
       </c>
       <c r="Q109" s="2">
         <v>0.0</v>
@@ -8080,7 +8080,7 @@
         <v>28.0</v>
       </c>
       <c r="S109" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="T109" s="2">
         <v>3.0</v>
@@ -8092,7 +8092,7 @@
         <v>0.0</v>
       </c>
       <c r="W109" s="2">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
@@ -8124,7 +8124,7 @@
         <v>754.0</v>
       </c>
       <c r="J110" s="2">
-        <v>415.0</v>
+        <v>436.0</v>
       </c>
       <c r="K110" s="2">
         <v>1.0</v>
@@ -8136,13 +8136,13 @@
         <v>0.0</v>
       </c>
       <c r="N110" s="2">
-        <v>415.0</v>
+        <v>436.0</v>
       </c>
       <c r="O110" s="2">
-        <v>184.0</v>
+        <v>199.0</v>
       </c>
       <c r="P110" s="2">
-        <v>231.0</v>
+        <v>237.0</v>
       </c>
       <c r="Q110" s="2">
         <v>0.0</v>
@@ -8195,7 +8195,7 @@
         <v>1027.0</v>
       </c>
       <c r="J111" s="2">
-        <v>767.0</v>
+        <v>772.0</v>
       </c>
       <c r="K111" s="2">
         <v>1.0</v>
@@ -8207,13 +8207,13 @@
         <v>0.0</v>
       </c>
       <c r="N111" s="2">
-        <v>767.0</v>
+        <v>772.0</v>
       </c>
       <c r="O111" s="2">
-        <v>339.0</v>
+        <v>343.0</v>
       </c>
       <c r="P111" s="2">
-        <v>425.0</v>
+        <v>426.0</v>
       </c>
       <c r="Q111" s="2">
         <v>3.0</v>
@@ -8266,7 +8266,7 @@
         <v>709.0</v>
       </c>
       <c r="J112" s="2">
-        <v>542.0</v>
+        <v>544.0</v>
       </c>
       <c r="K112" s="2">
         <v>1.0</v>
@@ -8278,13 +8278,13 @@
         <v>0.0</v>
       </c>
       <c r="N112" s="2">
-        <v>542.0</v>
+        <v>544.0</v>
       </c>
       <c r="O112" s="2">
-        <v>277.0</v>
+        <v>278.0</v>
       </c>
       <c r="P112" s="2">
-        <v>261.0</v>
+        <v>262.0</v>
       </c>
       <c r="Q112" s="2">
         <v>4.0</v>
@@ -8337,7 +8337,7 @@
         <v>921.0</v>
       </c>
       <c r="J113" s="2">
-        <v>545.0</v>
+        <v>570.0</v>
       </c>
       <c r="K113" s="2">
         <v>1.0</v>
@@ -8349,13 +8349,13 @@
         <v>0.0</v>
       </c>
       <c r="N113" s="2">
-        <v>545.0</v>
+        <v>570.0</v>
       </c>
       <c r="O113" s="2">
-        <v>180.0</v>
+        <v>187.0</v>
       </c>
       <c r="P113" s="2">
-        <v>365.0</v>
+        <v>383.0</v>
       </c>
       <c r="Q113" s="2">
         <v>0.0</v>
@@ -8550,7 +8550,7 @@
         <v>1148.0</v>
       </c>
       <c r="J116" s="2">
-        <v>629.0</v>
+        <v>652.0</v>
       </c>
       <c r="K116" s="2">
         <v>1.0</v>
@@ -8562,16 +8562,16 @@
         <v>1.0</v>
       </c>
       <c r="N116" s="2">
-        <v>628.0</v>
+        <v>651.0</v>
       </c>
       <c r="O116" s="2">
         <v>63.0</v>
       </c>
       <c r="P116" s="2">
-        <v>271.0</v>
+        <v>279.0</v>
       </c>
       <c r="Q116" s="2">
-        <v>295.0</v>
+        <v>310.0</v>
       </c>
       <c r="R116" s="2">
         <v>0.0</v>
@@ -8621,7 +8621,7 @@
         <v>1078.0</v>
       </c>
       <c r="J117" s="2">
-        <v>539.0</v>
+        <v>564.0</v>
       </c>
       <c r="K117" s="2">
         <v>1.0</v>
@@ -8633,13 +8633,13 @@
         <v>1.0</v>
       </c>
       <c r="N117" s="2">
-        <v>538.0</v>
+        <v>563.0</v>
       </c>
       <c r="O117" s="2">
-        <v>259.0</v>
+        <v>275.0</v>
       </c>
       <c r="P117" s="2">
-        <v>280.0</v>
+        <v>289.0</v>
       </c>
       <c r="Q117" s="2">
         <v>0.0</v>
@@ -8692,7 +8692,7 @@
         <v>1422.0</v>
       </c>
       <c r="J118" s="2">
-        <v>595.0</v>
+        <v>598.0</v>
       </c>
       <c r="K118" s="2">
         <v>1.0</v>
@@ -8704,10 +8704,10 @@
         <v>0.0</v>
       </c>
       <c r="N118" s="2">
-        <v>595.0</v>
+        <v>598.0</v>
       </c>
       <c r="O118" s="2">
-        <v>304.0</v>
+        <v>307.0</v>
       </c>
       <c r="P118" s="2">
         <v>289.0</v>
@@ -8763,7 +8763,7 @@
         <v>1084.0</v>
       </c>
       <c r="J119" s="2">
-        <v>617.0</v>
+        <v>656.0</v>
       </c>
       <c r="K119" s="2">
         <v>1.0</v>
@@ -8775,22 +8775,22 @@
         <v>0.0</v>
       </c>
       <c r="N119" s="2">
-        <v>617.0</v>
+        <v>656.0</v>
       </c>
       <c r="O119" s="2">
-        <v>352.0</v>
+        <v>383.0</v>
       </c>
       <c r="P119" s="2">
-        <v>260.0</v>
+        <v>268.0</v>
       </c>
       <c r="Q119" s="2">
         <v>5.0</v>
       </c>
       <c r="R119" s="2">
-        <v>38.0</v>
+        <v>47.0</v>
       </c>
       <c r="S119" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="T119" s="2">
         <v>0.0</v>
@@ -8802,7 +8802,7 @@
         <v>0.0</v>
       </c>
       <c r="W119" s="2">
-        <v>49.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
@@ -8834,7 +8834,7 @@
         <v>971.0</v>
       </c>
       <c r="J120" s="2">
-        <v>460.0</v>
+        <v>492.0</v>
       </c>
       <c r="K120" s="2">
         <v>1.0</v>
@@ -8846,22 +8846,22 @@
         <v>0.0</v>
       </c>
       <c r="N120" s="2">
-        <v>460.0</v>
+        <v>492.0</v>
       </c>
       <c r="O120" s="2">
-        <v>225.0</v>
+        <v>240.0</v>
       </c>
       <c r="P120" s="2">
-        <v>233.0</v>
+        <v>249.0</v>
       </c>
       <c r="Q120" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R120" s="2">
         <v>33.0</v>
       </c>
       <c r="S120" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T120" s="2">
         <v>0.0</v>
@@ -8873,7 +8873,7 @@
         <v>0.0</v>
       </c>
       <c r="W120" s="2">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
@@ -8905,7 +8905,7 @@
         <v>1425.0</v>
       </c>
       <c r="J121" s="2">
-        <v>538.0</v>
+        <v>589.0</v>
       </c>
       <c r="K121" s="2">
         <v>1.0</v>
@@ -8917,22 +8917,22 @@
         <v>0.0</v>
       </c>
       <c r="N121" s="2">
-        <v>538.0</v>
+        <v>589.0</v>
       </c>
       <c r="O121" s="2">
-        <v>313.0</v>
+        <v>358.0</v>
       </c>
       <c r="P121" s="2">
-        <v>225.0</v>
+        <v>231.0</v>
       </c>
       <c r="Q121" s="2">
         <v>0.0</v>
       </c>
       <c r="R121" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="S121" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="T121" s="2">
         <v>0.0</v>
@@ -8944,7 +8944,7 @@
         <v>0.0</v>
       </c>
       <c r="W121" s="2">
-        <v>7.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
@@ -8976,7 +8976,7 @@
         <v>939.0</v>
       </c>
       <c r="J122" s="2">
-        <v>516.0</v>
+        <v>529.0</v>
       </c>
       <c r="K122" s="2">
         <v>1.0</v>
@@ -8988,13 +8988,13 @@
         <v>4.0</v>
       </c>
       <c r="N122" s="2">
-        <v>512.0</v>
+        <v>525.0</v>
       </c>
       <c r="O122" s="2">
-        <v>280.0</v>
+        <v>289.0</v>
       </c>
       <c r="P122" s="2">
-        <v>221.0</v>
+        <v>225.0</v>
       </c>
       <c r="Q122" s="2">
         <v>15.0</v>
@@ -9189,7 +9189,7 @@
         <v>1432.0</v>
       </c>
       <c r="J125" s="2">
-        <v>1175.0</v>
+        <v>1188.0</v>
       </c>
       <c r="K125" s="2">
         <v>1.0</v>
@@ -9201,34 +9201,34 @@
         <v>0.0</v>
       </c>
       <c r="N125" s="2">
-        <v>1175.0</v>
+        <v>1188.0</v>
       </c>
       <c r="O125" s="2">
-        <v>534.0</v>
+        <v>539.0</v>
       </c>
       <c r="P125" s="2">
-        <v>581.0</v>
+        <v>589.0</v>
       </c>
       <c r="Q125" s="2">
         <v>60.0</v>
       </c>
       <c r="R125" s="2">
-        <v>0.0</v>
+        <v>67.0</v>
       </c>
       <c r="S125" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T125" s="2">
         <v>0.0</v>
       </c>
       <c r="U125" s="2">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="V125" s="2">
         <v>0.0</v>
       </c>
       <c r="W125" s="2">
-        <v>0.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
@@ -9260,7 +9260,7 @@
         <v>1151.0</v>
       </c>
       <c r="J126" s="2">
-        <v>752.0</v>
+        <v>771.0</v>
       </c>
       <c r="K126" s="2">
         <v>1.0</v>
@@ -9269,22 +9269,22 @@
         <v>1.0</v>
       </c>
       <c r="M126" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N126" s="2">
+        <v>771.0</v>
+      </c>
+      <c r="O126" s="2">
+        <v>407.0</v>
+      </c>
+      <c r="P126" s="2">
+        <v>362.0</v>
+      </c>
+      <c r="Q126" s="2">
         <v>2.0</v>
       </c>
-      <c r="N126" s="2">
-        <v>750.0</v>
-      </c>
-      <c r="O126" s="2">
-        <v>391.0</v>
-      </c>
-      <c r="P126" s="2">
-        <v>361.0</v>
-      </c>
-      <c r="Q126" s="2">
-        <v>0.0</v>
-      </c>
       <c r="R126" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="S126" s="2">
         <v>0.0</v>
@@ -9299,7 +9299,7 @@
         <v>0.0</v>
       </c>
       <c r="W126" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
@@ -9331,7 +9331,7 @@
         <v>1150.0</v>
       </c>
       <c r="J127" s="2">
-        <v>731.0</v>
+        <v>763.0</v>
       </c>
       <c r="K127" s="2">
         <v>1.0</v>
@@ -9343,13 +9343,13 @@
         <v>0.0</v>
       </c>
       <c r="N127" s="2">
-        <v>731.0</v>
+        <v>763.0</v>
       </c>
       <c r="O127" s="2">
-        <v>468.0</v>
+        <v>490.0</v>
       </c>
       <c r="P127" s="2">
-        <v>263.0</v>
+        <v>273.0</v>
       </c>
       <c r="Q127" s="2">
         <v>0.0</v>
@@ -9364,13 +9364,13 @@
         <v>2.0</v>
       </c>
       <c r="U127" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="V127" s="2">
         <v>0.0</v>
       </c>
       <c r="W127" s="2">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
@@ -9402,7 +9402,7 @@
         <v>1267.0</v>
       </c>
       <c r="J128" s="2">
-        <v>823.0</v>
+        <v>837.0</v>
       </c>
       <c r="K128" s="2">
         <v>1.0</v>
@@ -9414,13 +9414,13 @@
         <v>0.0</v>
       </c>
       <c r="N128" s="2">
-        <v>823.0</v>
+        <v>837.0</v>
       </c>
       <c r="O128" s="2">
-        <v>441.0</v>
+        <v>453.0</v>
       </c>
       <c r="P128" s="2">
-        <v>380.0</v>
+        <v>382.0</v>
       </c>
       <c r="Q128" s="2">
         <v>2.0</v>
@@ -9473,7 +9473,7 @@
         <v>1387.0</v>
       </c>
       <c r="J129" s="2">
-        <v>454.0</v>
+        <v>521.0</v>
       </c>
       <c r="K129" s="2">
         <v>1.0</v>
@@ -9485,13 +9485,13 @@
         <v>0.0</v>
       </c>
       <c r="N129" s="2">
-        <v>454.0</v>
+        <v>521.0</v>
       </c>
       <c r="O129" s="2">
-        <v>263.0</v>
+        <v>315.0</v>
       </c>
       <c r="P129" s="2">
-        <v>190.0</v>
+        <v>205.0</v>
       </c>
       <c r="Q129" s="2">
         <v>1.0</v>
@@ -9568,7 +9568,7 @@
         <v>30.0</v>
       </c>
       <c r="R130" s="2">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="S130" s="2">
         <v>0.0</v>
@@ -9583,7 +9583,7 @@
         <v>0.0</v>
       </c>
       <c r="W130" s="2">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
@@ -9615,7 +9615,7 @@
         <v>865.0</v>
       </c>
       <c r="J131" s="2">
-        <v>537.0</v>
+        <v>544.0</v>
       </c>
       <c r="K131" s="2">
         <v>1.0</v>
@@ -9627,13 +9627,13 @@
         <v>5.0</v>
       </c>
       <c r="N131" s="2">
-        <v>532.0</v>
+        <v>539.0</v>
       </c>
       <c r="O131" s="2">
-        <v>285.0</v>
+        <v>289.0</v>
       </c>
       <c r="P131" s="2">
-        <v>235.0</v>
+        <v>238.0</v>
       </c>
       <c r="Q131" s="2">
         <v>17.0</v>
@@ -9686,7 +9686,7 @@
         <v>1427.0</v>
       </c>
       <c r="J132" s="2">
-        <v>527.0</v>
+        <v>536.0</v>
       </c>
       <c r="K132" s="2">
         <v>1.0</v>
@@ -9698,13 +9698,13 @@
         <v>4.0</v>
       </c>
       <c r="N132" s="2">
-        <v>523.0</v>
+        <v>532.0</v>
       </c>
       <c r="O132" s="2">
-        <v>224.0</v>
+        <v>227.0</v>
       </c>
       <c r="P132" s="2">
-        <v>294.0</v>
+        <v>300.0</v>
       </c>
       <c r="Q132" s="2">
         <v>9.0</v>
@@ -9757,7 +9757,7 @@
         <v>1330.0</v>
       </c>
       <c r="J133" s="2">
-        <v>717.0</v>
+        <v>738.0</v>
       </c>
       <c r="K133" s="2">
         <v>1.0</v>
@@ -9769,13 +9769,13 @@
         <v>0.0</v>
       </c>
       <c r="N133" s="2">
-        <v>717.0</v>
+        <v>738.0</v>
       </c>
       <c r="O133" s="2">
-        <v>379.0</v>
+        <v>394.0</v>
       </c>
       <c r="P133" s="2">
-        <v>327.0</v>
+        <v>333.0</v>
       </c>
       <c r="Q133" s="2">
         <v>11.0</v>
@@ -9828,7 +9828,7 @@
         <v>1343.0</v>
       </c>
       <c r="J134" s="2">
-        <v>1082.0</v>
+        <v>1101.0</v>
       </c>
       <c r="K134" s="2">
         <v>1.0</v>
@@ -9840,34 +9840,34 @@
         <v>1.0</v>
       </c>
       <c r="N134" s="2">
-        <v>1081.0</v>
+        <v>1100.0</v>
       </c>
       <c r="O134" s="2">
-        <v>697.0</v>
+        <v>710.0</v>
       </c>
       <c r="P134" s="2">
         <v>383.0</v>
       </c>
       <c r="Q134" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="R134" s="2">
         <v>43.0</v>
       </c>
       <c r="S134" s="2">
-        <v>43.0</v>
+        <v>56.0</v>
       </c>
       <c r="T134" s="2">
         <v>0.0</v>
       </c>
       <c r="U134" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="V134" s="2">
         <v>2.0</v>
       </c>
       <c r="W134" s="2">
-        <v>97.0</v>
+        <v>113.0</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1">
@@ -9899,7 +9899,7 @@
         <v>1247.0</v>
       </c>
       <c r="J135" s="2">
-        <v>741.0</v>
+        <v>772.0</v>
       </c>
       <c r="K135" s="2">
         <v>1.0</v>
@@ -9911,13 +9911,13 @@
         <v>1.0</v>
       </c>
       <c r="N135" s="2">
-        <v>740.0</v>
+        <v>771.0</v>
       </c>
       <c r="O135" s="2">
-        <v>363.0</v>
+        <v>383.0</v>
       </c>
       <c r="P135" s="2">
-        <v>296.0</v>
+        <v>307.0</v>
       </c>
       <c r="Q135" s="2">
         <v>82.0</v>
@@ -9970,7 +9970,7 @@
         <v>1122.0</v>
       </c>
       <c r="J136" s="2">
-        <v>622.0</v>
+        <v>623.0</v>
       </c>
       <c r="K136" s="2">
         <v>1.0</v>
@@ -9982,10 +9982,10 @@
         <v>0.0</v>
       </c>
       <c r="N136" s="2">
-        <v>622.0</v>
+        <v>623.0</v>
       </c>
       <c r="O136" s="2">
-        <v>335.0</v>
+        <v>336.0</v>
       </c>
       <c r="P136" s="2">
         <v>277.0</v>
@@ -10041,7 +10041,7 @@
         <v>1211.0</v>
       </c>
       <c r="J137" s="2">
-        <v>483.0</v>
+        <v>524.0</v>
       </c>
       <c r="K137" s="2">
         <v>1.0</v>
@@ -10053,13 +10053,13 @@
         <v>0.0</v>
       </c>
       <c r="N137" s="2">
-        <v>483.0</v>
+        <v>524.0</v>
       </c>
       <c r="O137" s="2">
-        <v>196.0</v>
+        <v>221.0</v>
       </c>
       <c r="P137" s="2">
-        <v>273.0</v>
+        <v>289.0</v>
       </c>
       <c r="Q137" s="2">
         <v>14.0</v>
@@ -10068,7 +10068,7 @@
         <v>30.0</v>
       </c>
       <c r="S137" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="T137" s="2">
         <v>0.0</v>
@@ -10080,7 +10080,7 @@
         <v>0.0</v>
       </c>
       <c r="W137" s="2">
-        <v>38.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
@@ -10183,7 +10183,7 @@
         <v>1300.0</v>
       </c>
       <c r="J139" s="2">
-        <v>750.0</v>
+        <v>754.0</v>
       </c>
       <c r="K139" s="2">
         <v>1.0</v>
@@ -10192,16 +10192,16 @@
         <v>1.0</v>
       </c>
       <c r="M139" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N139" s="2">
-        <v>749.0</v>
+        <v>754.0</v>
       </c>
       <c r="O139" s="2">
-        <v>449.0</v>
+        <v>452.0</v>
       </c>
       <c r="P139" s="2">
-        <v>280.0</v>
+        <v>281.0</v>
       </c>
       <c r="Q139" s="2">
         <v>21.0</v>
@@ -10254,7 +10254,7 @@
         <v>1236.0</v>
       </c>
       <c r="J140" s="2">
-        <v>618.0</v>
+        <v>627.0</v>
       </c>
       <c r="K140" s="2">
         <v>1.0</v>
@@ -10266,13 +10266,13 @@
         <v>0.0</v>
       </c>
       <c r="N140" s="2">
-        <v>618.0</v>
+        <v>627.0</v>
       </c>
       <c r="O140" s="2">
-        <v>305.0</v>
+        <v>310.0</v>
       </c>
       <c r="P140" s="2">
-        <v>312.0</v>
+        <v>316.0</v>
       </c>
       <c r="Q140" s="2">
         <v>1.0</v>
@@ -10325,7 +10325,7 @@
         <v>1244.0</v>
       </c>
       <c r="J141" s="2">
-        <v>594.0</v>
+        <v>649.0</v>
       </c>
       <c r="K141" s="2">
         <v>1.0</v>
@@ -10337,13 +10337,13 @@
         <v>1.0</v>
       </c>
       <c r="N141" s="2">
-        <v>593.0</v>
+        <v>648.0</v>
       </c>
       <c r="O141" s="2">
-        <v>334.0</v>
+        <v>378.0</v>
       </c>
       <c r="P141" s="2">
-        <v>260.0</v>
+        <v>271.0</v>
       </c>
       <c r="Q141" s="2">
         <v>0.0</v>
@@ -10358,13 +10358,13 @@
         <v>0.0</v>
       </c>
       <c r="U141" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V141" s="2">
         <v>0.0</v>
       </c>
       <c r="W141" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
@@ -10420,13 +10420,13 @@
         <v>0.0</v>
       </c>
       <c r="R142" s="2">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
       <c r="S142" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="T142" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="U142" s="2">
         <v>0.0</v>
@@ -10435,7 +10435,7 @@
         <v>0.0</v>
       </c>
       <c r="W142" s="2">
-        <v>4.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
@@ -10467,7 +10467,7 @@
         <v>1469.0</v>
       </c>
       <c r="J143" s="2">
-        <v>579.0</v>
+        <v>604.0</v>
       </c>
       <c r="K143" s="2">
         <v>1.0</v>
@@ -10479,13 +10479,13 @@
         <v>1.0</v>
       </c>
       <c r="N143" s="2">
-        <v>578.0</v>
+        <v>603.0</v>
       </c>
       <c r="O143" s="2">
-        <v>354.0</v>
+        <v>371.0</v>
       </c>
       <c r="P143" s="2">
-        <v>225.0</v>
+        <v>233.0</v>
       </c>
       <c r="Q143" s="2">
         <v>0.0</v>
@@ -10538,7 +10538,7 @@
         <v>1487.0</v>
       </c>
       <c r="J144" s="2">
-        <v>705.0</v>
+        <v>723.0</v>
       </c>
       <c r="K144" s="2">
         <v>1.0</v>
@@ -10550,13 +10550,13 @@
         <v>0.0</v>
       </c>
       <c r="N144" s="2">
-        <v>705.0</v>
+        <v>723.0</v>
       </c>
       <c r="O144" s="2">
-        <v>362.0</v>
+        <v>375.0</v>
       </c>
       <c r="P144" s="2">
-        <v>343.0</v>
+        <v>348.0</v>
       </c>
       <c r="Q144" s="2">
         <v>0.0</v>
@@ -10609,7 +10609,7 @@
         <v>1012.0</v>
       </c>
       <c r="J145" s="2">
-        <v>578.0</v>
+        <v>579.0</v>
       </c>
       <c r="K145" s="2">
         <v>1.0</v>
@@ -10621,10 +10621,10 @@
         <v>0.0</v>
       </c>
       <c r="N145" s="2">
-        <v>578.0</v>
+        <v>579.0</v>
       </c>
       <c r="O145" s="2">
-        <v>231.0</v>
+        <v>232.0</v>
       </c>
       <c r="P145" s="2">
         <v>328.0</v>
@@ -10639,7 +10639,7 @@
         <v>12.0</v>
       </c>
       <c r="T145" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U145" s="2">
         <v>8.0</v>
@@ -10648,7 +10648,7 @@
         <v>1.0</v>
       </c>
       <c r="W145" s="2">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1">
@@ -10680,7 +10680,7 @@
         <v>863.0</v>
       </c>
       <c r="J146" s="2">
-        <v>359.0</v>
+        <v>367.0</v>
       </c>
       <c r="K146" s="2">
         <v>1.0</v>
@@ -10692,19 +10692,19 @@
         <v>2.0</v>
       </c>
       <c r="N146" s="2">
-        <v>357.0</v>
+        <v>365.0</v>
       </c>
       <c r="O146" s="2">
-        <v>154.0</v>
+        <v>161.0</v>
       </c>
       <c r="P146" s="2">
-        <v>205.0</v>
+        <v>206.0</v>
       </c>
       <c r="Q146" s="2">
         <v>0.0</v>
       </c>
       <c r="R146" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="S146" s="2">
         <v>2.0</v>
@@ -10719,7 +10719,7 @@
         <v>0.0</v>
       </c>
       <c r="W146" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1">
@@ -10893,7 +10893,7 @@
         <v>1218.0</v>
       </c>
       <c r="J149" s="2">
-        <v>442.0</v>
+        <v>492.0</v>
       </c>
       <c r="K149" s="2">
         <v>1.0</v>
@@ -10905,16 +10905,16 @@
         <v>0.0</v>
       </c>
       <c r="N149" s="2">
-        <v>442.0</v>
+        <v>492.0</v>
       </c>
       <c r="O149" s="2">
-        <v>250.0</v>
+        <v>280.0</v>
       </c>
       <c r="P149" s="2">
-        <v>189.0</v>
+        <v>208.0</v>
       </c>
       <c r="Q149" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R149" s="2">
         <v>0.0</v>
@@ -11035,7 +11035,7 @@
         <v>695.0</v>
       </c>
       <c r="J151" s="2">
-        <v>395.0</v>
+        <v>401.0</v>
       </c>
       <c r="K151" s="2">
         <v>1.0</v>
@@ -11047,19 +11047,19 @@
         <v>0.0</v>
       </c>
       <c r="N151" s="2">
-        <v>395.0</v>
+        <v>401.0</v>
       </c>
       <c r="O151" s="2">
-        <v>195.0</v>
+        <v>199.0</v>
       </c>
       <c r="P151" s="2">
-        <v>200.0</v>
+        <v>202.0</v>
       </c>
       <c r="Q151" s="2">
         <v>0.0</v>
       </c>
       <c r="R151" s="2">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="S151" s="2">
         <v>0.0</v>
@@ -11074,7 +11074,7 @@
         <v>0.0</v>
       </c>
       <c r="W151" s="2">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
@@ -11106,7 +11106,7 @@
         <v>942.0</v>
       </c>
       <c r="J152" s="2">
-        <v>541.0</v>
+        <v>553.0</v>
       </c>
       <c r="K152" s="2">
         <v>1.0</v>
@@ -11118,13 +11118,13 @@
         <v>1.0</v>
       </c>
       <c r="N152" s="2">
-        <v>540.0</v>
+        <v>552.0</v>
       </c>
       <c r="O152" s="2">
-        <v>263.0</v>
+        <v>269.0</v>
       </c>
       <c r="P152" s="2">
-        <v>278.0</v>
+        <v>284.0</v>
       </c>
       <c r="Q152" s="2">
         <v>0.0</v>
@@ -11177,7 +11177,7 @@
         <v>1018.0</v>
       </c>
       <c r="J153" s="2">
-        <v>767.0</v>
+        <v>768.0</v>
       </c>
       <c r="K153" s="2">
         <v>1.0</v>
@@ -11189,10 +11189,10 @@
         <v>0.0</v>
       </c>
       <c r="N153" s="2">
-        <v>767.0</v>
+        <v>768.0</v>
       </c>
       <c r="O153" s="2">
-        <v>373.0</v>
+        <v>374.0</v>
       </c>
       <c r="P153" s="2">
         <v>394.0</v>
@@ -11248,7 +11248,7 @@
         <v>999.0</v>
       </c>
       <c r="J154" s="2">
-        <v>546.0</v>
+        <v>565.0</v>
       </c>
       <c r="K154" s="2">
         <v>1.0</v>
@@ -11260,16 +11260,16 @@
         <v>0.0</v>
       </c>
       <c r="N154" s="2">
-        <v>546.0</v>
+        <v>565.0</v>
       </c>
       <c r="O154" s="2">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="P154" s="2">
-        <v>307.0</v>
+        <v>312.0</v>
       </c>
       <c r="Q154" s="2">
-        <v>209.0</v>
+        <v>222.0</v>
       </c>
       <c r="R154" s="2">
         <v>0.0</v>
@@ -11319,7 +11319,7 @@
         <v>1180.0</v>
       </c>
       <c r="J155" s="2">
-        <v>722.0</v>
+        <v>752.0</v>
       </c>
       <c r="K155" s="2">
         <v>1.0</v>
@@ -11331,13 +11331,13 @@
         <v>0.0</v>
       </c>
       <c r="N155" s="2">
-        <v>722.0</v>
+        <v>752.0</v>
       </c>
       <c r="O155" s="2">
-        <v>354.0</v>
+        <v>366.0</v>
       </c>
       <c r="P155" s="2">
-        <v>368.0</v>
+        <v>386.0</v>
       </c>
       <c r="Q155" s="2">
         <v>0.0</v>
@@ -11532,7 +11532,7 @@
         <v>1353.0</v>
       </c>
       <c r="J158" s="2">
-        <v>661.0</v>
+        <v>691.0</v>
       </c>
       <c r="K158" s="2">
         <v>1.0</v>
@@ -11544,13 +11544,13 @@
         <v>0.0</v>
       </c>
       <c r="N158" s="2">
-        <v>661.0</v>
+        <v>691.0</v>
       </c>
       <c r="O158" s="2">
-        <v>304.0</v>
+        <v>315.0</v>
       </c>
       <c r="P158" s="2">
-        <v>357.0</v>
+        <v>376.0</v>
       </c>
       <c r="Q158" s="2">
         <v>0.0</v>
@@ -11603,7 +11603,7 @@
         <v>1153.0</v>
       </c>
       <c r="J159" s="2">
-        <v>719.0</v>
+        <v>734.0</v>
       </c>
       <c r="K159" s="2">
         <v>1.0</v>
@@ -11615,13 +11615,13 @@
         <v>1.0</v>
       </c>
       <c r="N159" s="2">
-        <v>718.0</v>
+        <v>733.0</v>
       </c>
       <c r="O159" s="2">
-        <v>409.0</v>
+        <v>423.0</v>
       </c>
       <c r="P159" s="2">
-        <v>310.0</v>
+        <v>311.0</v>
       </c>
       <c r="Q159" s="2">
         <v>0.0</v>
@@ -11674,7 +11674,7 @@
         <v>1283.0</v>
       </c>
       <c r="J160" s="2">
-        <v>825.0</v>
+        <v>835.0</v>
       </c>
       <c r="K160" s="2">
         <v>1.0</v>
@@ -11686,13 +11686,13 @@
         <v>0.0</v>
       </c>
       <c r="N160" s="2">
-        <v>825.0</v>
+        <v>835.0</v>
       </c>
       <c r="O160" s="2">
-        <v>410.0</v>
+        <v>413.0</v>
       </c>
       <c r="P160" s="2">
-        <v>415.0</v>
+        <v>422.0</v>
       </c>
       <c r="Q160" s="2">
         <v>0.0</v>
@@ -11745,7 +11745,7 @@
         <v>1401.0</v>
       </c>
       <c r="J161" s="2">
-        <v>863.0</v>
+        <v>868.0</v>
       </c>
       <c r="K161" s="2">
         <v>1.0</v>
@@ -11757,19 +11757,19 @@
         <v>0.0</v>
       </c>
       <c r="N161" s="2">
-        <v>863.0</v>
+        <v>868.0</v>
       </c>
       <c r="O161" s="2">
-        <v>451.0</v>
+        <v>455.0</v>
       </c>
       <c r="P161" s="2">
-        <v>404.0</v>
+        <v>405.0</v>
       </c>
       <c r="Q161" s="2">
         <v>8.0</v>
       </c>
       <c r="R161" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S161" s="2">
         <v>0.0</v>
@@ -11784,7 +11784,7 @@
         <v>0.0</v>
       </c>
       <c r="W161" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="162" ht="15.75" customHeight="1">
@@ -11816,7 +11816,7 @@
         <v>1184.0</v>
       </c>
       <c r="J162" s="2">
-        <v>731.0</v>
+        <v>737.0</v>
       </c>
       <c r="K162" s="2">
         <v>1.0</v>
@@ -11828,16 +11828,16 @@
         <v>1.0</v>
       </c>
       <c r="N162" s="2">
-        <v>730.0</v>
+        <v>736.0</v>
       </c>
       <c r="O162" s="2">
         <v>13.0</v>
       </c>
       <c r="P162" s="2">
-        <v>179.0</v>
+        <v>181.0</v>
       </c>
       <c r="Q162" s="2">
-        <v>539.0</v>
+        <v>543.0</v>
       </c>
       <c r="R162" s="2">
         <v>0.0</v>
@@ -11887,7 +11887,7 @@
         <v>1298.0</v>
       </c>
       <c r="J163" s="2">
-        <v>690.0</v>
+        <v>696.0</v>
       </c>
       <c r="K163" s="2">
         <v>1.0</v>
@@ -11899,22 +11899,22 @@
         <v>0.0</v>
       </c>
       <c r="N163" s="2">
-        <v>690.0</v>
+        <v>696.0</v>
       </c>
       <c r="O163" s="2">
         <v>10.0</v>
       </c>
       <c r="P163" s="2">
-        <v>309.0</v>
+        <v>310.0</v>
       </c>
       <c r="Q163" s="2">
-        <v>371.0</v>
+        <v>376.0</v>
       </c>
       <c r="R163" s="2">
         <v>0.0</v>
       </c>
       <c r="S163" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="T163" s="2">
         <v>0.0</v>
@@ -11926,7 +11926,7 @@
         <v>0.0</v>
       </c>
       <c r="W163" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
@@ -11958,7 +11958,7 @@
         <v>1054.0</v>
       </c>
       <c r="J164" s="2">
-        <v>682.0</v>
+        <v>685.0</v>
       </c>
       <c r="K164" s="2">
         <v>1.0</v>
@@ -11970,13 +11970,13 @@
         <v>1.0</v>
       </c>
       <c r="N164" s="2">
-        <v>681.0</v>
+        <v>684.0</v>
       </c>
       <c r="O164" s="2">
         <v>19.0</v>
       </c>
       <c r="P164" s="2">
-        <v>294.0</v>
+        <v>297.0</v>
       </c>
       <c r="Q164" s="2">
         <v>369.0</v>
@@ -12100,7 +12100,7 @@
         <v>932.0</v>
       </c>
       <c r="J166" s="2">
-        <v>566.0</v>
+        <v>570.0</v>
       </c>
       <c r="K166" s="2">
         <v>1.0</v>
@@ -12112,22 +12112,22 @@
         <v>0.0</v>
       </c>
       <c r="N166" s="2">
-        <v>566.0</v>
+        <v>570.0</v>
       </c>
       <c r="O166" s="2">
-        <v>310.0</v>
+        <v>312.0</v>
       </c>
       <c r="P166" s="2">
-        <v>256.0</v>
+        <v>258.0</v>
       </c>
       <c r="Q166" s="2">
         <v>0.0</v>
       </c>
       <c r="R166" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="S166" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="T166" s="2">
         <v>0.0</v>
@@ -12139,7 +12139,7 @@
         <v>0.0</v>
       </c>
       <c r="W166" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
@@ -12171,7 +12171,7 @@
         <v>667.0</v>
       </c>
       <c r="J167" s="2">
-        <v>541.0</v>
+        <v>563.0</v>
       </c>
       <c r="K167" s="2">
         <v>1.0</v>
@@ -12183,16 +12183,16 @@
         <v>0.0</v>
       </c>
       <c r="N167" s="2">
-        <v>541.0</v>
+        <v>563.0</v>
       </c>
       <c r="O167" s="2">
-        <v>265.0</v>
+        <v>280.0</v>
       </c>
       <c r="P167" s="2">
-        <v>276.0</v>
+        <v>282.0</v>
       </c>
       <c r="Q167" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R167" s="2">
         <v>26.0</v>
@@ -12313,7 +12313,7 @@
         <v>503.0</v>
       </c>
       <c r="J169" s="2">
-        <v>381.0</v>
+        <v>388.0</v>
       </c>
       <c r="K169" s="2">
         <v>1.0</v>
@@ -12325,13 +12325,13 @@
         <v>0.0</v>
       </c>
       <c r="N169" s="2">
-        <v>381.0</v>
+        <v>388.0</v>
       </c>
       <c r="O169" s="2">
-        <v>173.0</v>
+        <v>179.0</v>
       </c>
       <c r="P169" s="2">
-        <v>200.0</v>
+        <v>201.0</v>
       </c>
       <c r="Q169" s="2">
         <v>8.0</v>
@@ -12455,7 +12455,7 @@
         <v>576.0</v>
       </c>
       <c r="J171" s="2">
-        <v>386.0</v>
+        <v>409.0</v>
       </c>
       <c r="K171" s="2">
         <v>1.0</v>
@@ -12467,13 +12467,13 @@
         <v>0.0</v>
       </c>
       <c r="N171" s="2">
-        <v>386.0</v>
+        <v>409.0</v>
       </c>
       <c r="O171" s="2">
-        <v>209.0</v>
+        <v>227.0</v>
       </c>
       <c r="P171" s="2">
-        <v>177.0</v>
+        <v>182.0</v>
       </c>
       <c r="Q171" s="2">
         <v>0.0</v>
@@ -12597,7 +12597,7 @@
         <v>1266.0</v>
       </c>
       <c r="J173" s="2">
-        <v>907.0</v>
+        <v>923.0</v>
       </c>
       <c r="K173" s="2">
         <v>1.0</v>
@@ -12609,10 +12609,10 @@
         <v>0.0</v>
       </c>
       <c r="N173" s="2">
-        <v>907.0</v>
+        <v>923.0</v>
       </c>
       <c r="O173" s="2">
-        <v>487.0</v>
+        <v>503.0</v>
       </c>
       <c r="P173" s="2">
         <v>420.0</v>
@@ -12621,13 +12621,13 @@
         <v>0.0</v>
       </c>
       <c r="R173" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="S173" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T173" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U173" s="2">
         <v>0.0</v>
@@ -12636,7 +12636,7 @@
         <v>0.0</v>
       </c>
       <c r="W173" s="2">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
@@ -12810,7 +12810,7 @@
         <v>1045.0</v>
       </c>
       <c r="J176" s="2">
-        <v>441.0</v>
+        <v>475.0</v>
       </c>
       <c r="K176" s="2">
         <v>1.0</v>
@@ -12822,13 +12822,13 @@
         <v>0.0</v>
       </c>
       <c r="N176" s="2">
-        <v>441.0</v>
+        <v>475.0</v>
       </c>
       <c r="O176" s="2">
-        <v>173.0</v>
+        <v>193.0</v>
       </c>
       <c r="P176" s="2">
-        <v>268.0</v>
+        <v>282.0</v>
       </c>
       <c r="Q176" s="2">
         <v>0.0</v>
@@ -12843,13 +12843,13 @@
         <v>0.0</v>
       </c>
       <c r="U176" s="2">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="V176" s="2">
         <v>2.0</v>
       </c>
       <c r="W176" s="2">
-        <v>78.0</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
@@ -12881,7 +12881,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" s="2">
-        <v>410.0</v>
+        <v>422.0</v>
       </c>
       <c r="K177" s="2">
         <v>1.0</v>
@@ -12893,13 +12893,13 @@
         <v>0.0</v>
       </c>
       <c r="N177" s="2">
-        <v>410.0</v>
+        <v>422.0</v>
       </c>
       <c r="O177" s="2">
-        <v>197.0</v>
+        <v>207.0</v>
       </c>
       <c r="P177" s="2">
-        <v>213.0</v>
+        <v>215.0</v>
       </c>
       <c r="Q177" s="2">
         <v>0.0</v>
@@ -12952,7 +12952,7 @@
         <v>1008.0</v>
       </c>
       <c r="J178" s="2">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="K178" s="2">
         <v>1.0</v>
@@ -12964,13 +12964,13 @@
         <v>0.0</v>
       </c>
       <c r="N178" s="2">
-        <v>324.0</v>
+        <v>331.0</v>
       </c>
       <c r="O178" s="2">
-        <v>149.0</v>
+        <v>152.0</v>
       </c>
       <c r="P178" s="2">
-        <v>174.0</v>
+        <v>178.0</v>
       </c>
       <c r="Q178" s="2">
         <v>1.0</v>
@@ -12985,13 +12985,13 @@
         <v>0.0</v>
       </c>
       <c r="U178" s="2">
-        <v>25.0</v>
+        <v>47.0</v>
       </c>
       <c r="V178" s="2">
         <v>0.0</v>
       </c>
       <c r="W178" s="2">
-        <v>38.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1">
@@ -13047,7 +13047,7 @@
         <v>1.0</v>
       </c>
       <c r="R179" s="2">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="S179" s="2">
         <v>7.0</v>
@@ -13062,7 +13062,7 @@
         <v>0.0</v>
       </c>
       <c r="W179" s="2">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="180" ht="15.75" customHeight="1">
@@ -13094,7 +13094,7 @@
         <v>781.0</v>
       </c>
       <c r="J180" s="2">
-        <v>359.0</v>
+        <v>375.0</v>
       </c>
       <c r="K180" s="2">
         <v>1.0</v>
@@ -13106,13 +13106,13 @@
         <v>0.0</v>
       </c>
       <c r="N180" s="2">
-        <v>359.0</v>
+        <v>375.0</v>
       </c>
       <c r="O180" s="2">
-        <v>188.0</v>
+        <v>198.0</v>
       </c>
       <c r="P180" s="2">
-        <v>171.0</v>
+        <v>177.0</v>
       </c>
       <c r="Q180" s="2">
         <v>0.0</v>
@@ -13189,22 +13189,22 @@
         <v>0.0</v>
       </c>
       <c r="R181" s="2">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="S181" s="2">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="T181" s="2">
         <v>0.0</v>
       </c>
       <c r="U181" s="2">
-        <v>70.0</v>
+        <v>90.0</v>
       </c>
       <c r="V181" s="2">
         <v>0.0</v>
       </c>
       <c r="W181" s="2">
-        <v>87.0</v>
+        <v>115.0</v>
       </c>
     </row>
     <row r="182" ht="15.75" customHeight="1">
@@ -13236,7 +13236,7 @@
         <v>753.0</v>
       </c>
       <c r="J182" s="2">
-        <v>572.0</v>
+        <v>586.0</v>
       </c>
       <c r="K182" s="2">
         <v>1.0</v>
@@ -13248,13 +13248,13 @@
         <v>0.0</v>
       </c>
       <c r="N182" s="2">
-        <v>572.0</v>
+        <v>586.0</v>
       </c>
       <c r="O182" s="2">
-        <v>257.0</v>
+        <v>266.0</v>
       </c>
       <c r="P182" s="2">
-        <v>314.0</v>
+        <v>319.0</v>
       </c>
       <c r="Q182" s="2">
         <v>1.0</v>
@@ -13263,7 +13263,7 @@
         <v>21.0</v>
       </c>
       <c r="S182" s="2">
-        <v>34.0</v>
+        <v>38.0</v>
       </c>
       <c r="T182" s="2">
         <v>6.0</v>
@@ -13275,7 +13275,7 @@
         <v>0.0</v>
       </c>
       <c r="W182" s="2">
-        <v>63.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="183" ht="15.75" customHeight="1">
@@ -13449,7 +13449,7 @@
         <v>1000.0</v>
       </c>
       <c r="J185" s="2">
-        <v>639.0</v>
+        <v>666.0</v>
       </c>
       <c r="K185" s="2">
         <v>1.0</v>
@@ -13461,13 +13461,13 @@
         <v>0.0</v>
       </c>
       <c r="N185" s="2">
-        <v>639.0</v>
+        <v>666.0</v>
       </c>
       <c r="O185" s="2">
-        <v>331.0</v>
+        <v>350.0</v>
       </c>
       <c r="P185" s="2">
-        <v>308.0</v>
+        <v>316.0</v>
       </c>
       <c r="Q185" s="2">
         <v>0.0</v>
@@ -13520,7 +13520,7 @@
         <v>1067.0</v>
       </c>
       <c r="J186" s="2">
-        <v>634.0</v>
+        <v>677.0</v>
       </c>
       <c r="K186" s="2">
         <v>1.0</v>
@@ -13532,16 +13532,16 @@
         <v>0.0</v>
       </c>
       <c r="N186" s="2">
-        <v>634.0</v>
+        <v>677.0</v>
       </c>
       <c r="O186" s="2">
         <v>118.0</v>
       </c>
       <c r="P186" s="2">
-        <v>293.0</v>
+        <v>307.0</v>
       </c>
       <c r="Q186" s="2">
-        <v>223.0</v>
+        <v>252.0</v>
       </c>
       <c r="R186" s="2">
         <v>6.0</v>
@@ -13591,7 +13591,7 @@
         <v>990.0</v>
       </c>
       <c r="J187" s="2">
-        <v>665.0</v>
+        <v>679.0</v>
       </c>
       <c r="K187" s="2">
         <v>1.0</v>
@@ -13603,13 +13603,13 @@
         <v>0.0</v>
       </c>
       <c r="N187" s="2">
-        <v>665.0</v>
+        <v>679.0</v>
       </c>
       <c r="O187" s="2">
-        <v>405.0</v>
+        <v>414.0</v>
       </c>
       <c r="P187" s="2">
-        <v>260.0</v>
+        <v>265.0</v>
       </c>
       <c r="Q187" s="2">
         <v>0.0</v>
@@ -13662,7 +13662,7 @@
         <v>1017.0</v>
       </c>
       <c r="J188" s="2">
-        <v>567.0</v>
+        <v>569.0</v>
       </c>
       <c r="K188" s="2">
         <v>1.0</v>
@@ -13674,13 +13674,13 @@
         <v>0.0</v>
       </c>
       <c r="N188" s="2">
-        <v>567.0</v>
+        <v>569.0</v>
       </c>
       <c r="O188" s="2">
         <v>174.0</v>
       </c>
       <c r="P188" s="2">
-        <v>335.0</v>
+        <v>337.0</v>
       </c>
       <c r="Q188" s="2">
         <v>58.0</v>
@@ -14159,7 +14159,7 @@
         <v>556.0</v>
       </c>
       <c r="J195" s="2">
-        <v>344.0</v>
+        <v>346.0</v>
       </c>
       <c r="K195" s="2">
         <v>1.0</v>
@@ -14171,16 +14171,16 @@
         <v>0.0</v>
       </c>
       <c r="N195" s="2">
-        <v>344.0</v>
+        <v>346.0</v>
       </c>
       <c r="O195" s="2">
         <v>74.0</v>
       </c>
       <c r="P195" s="2">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
       <c r="Q195" s="2">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="R195" s="2">
         <v>0.0</v>
@@ -14230,7 +14230,7 @@
         <v>1391.0</v>
       </c>
       <c r="J196" s="2">
-        <v>1105.0</v>
+        <v>1110.0</v>
       </c>
       <c r="K196" s="2">
         <v>1.0</v>
@@ -14242,7 +14242,7 @@
         <v>0.0</v>
       </c>
       <c r="N196" s="2">
-        <v>1105.0</v>
+        <v>1110.0</v>
       </c>
       <c r="O196" s="2">
         <v>431.0</v>
@@ -14251,7 +14251,7 @@
         <v>488.0</v>
       </c>
       <c r="Q196" s="2">
-        <v>186.0</v>
+        <v>191.0</v>
       </c>
       <c r="R196" s="2">
         <v>0.0</v>
@@ -14443,7 +14443,7 @@
         <v>1015.0</v>
       </c>
       <c r="J199" s="2">
-        <v>722.0</v>
+        <v>736.0</v>
       </c>
       <c r="K199" s="2">
         <v>1.0</v>
@@ -14455,19 +14455,19 @@
         <v>0.0</v>
       </c>
       <c r="N199" s="2">
-        <v>722.0</v>
+        <v>736.0</v>
       </c>
       <c r="O199" s="2">
-        <v>311.0</v>
+        <v>320.0</v>
       </c>
       <c r="P199" s="2">
-        <v>411.0</v>
+        <v>416.0</v>
       </c>
       <c r="Q199" s="2">
         <v>0.0</v>
       </c>
       <c r="R199" s="2">
-        <v>41.0</v>
+        <v>52.0</v>
       </c>
       <c r="S199" s="2">
         <v>0.0</v>
@@ -14482,7 +14482,7 @@
         <v>1.0</v>
       </c>
       <c r="W199" s="2">
-        <v>42.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="200" ht="15.75" customHeight="1">
@@ -14514,7 +14514,7 @@
         <v>704.0</v>
       </c>
       <c r="J200" s="2">
-        <v>480.0</v>
+        <v>486.0</v>
       </c>
       <c r="K200" s="2">
         <v>1.0</v>
@@ -14526,22 +14526,22 @@
         <v>0.0</v>
       </c>
       <c r="N200" s="2">
-        <v>480.0</v>
+        <v>486.0</v>
       </c>
       <c r="O200" s="2">
-        <v>297.0</v>
+        <v>299.0</v>
       </c>
       <c r="P200" s="2">
-        <v>180.0</v>
+        <v>184.0</v>
       </c>
       <c r="Q200" s="2">
         <v>3.0</v>
       </c>
       <c r="R200" s="2">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="S200" s="2">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
       <c r="T200" s="2">
         <v>1.0</v>
@@ -14553,7 +14553,7 @@
         <v>0.0</v>
       </c>
       <c r="W200" s="2">
-        <v>43.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="201" ht="15.75" customHeight="1">
@@ -14656,7 +14656,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" s="2">
-        <v>396.0</v>
+        <v>434.0</v>
       </c>
       <c r="K202" s="2">
         <v>1.0</v>
@@ -14668,13 +14668,13 @@
         <v>0.0</v>
       </c>
       <c r="N202" s="2">
-        <v>396.0</v>
+        <v>434.0</v>
       </c>
       <c r="O202" s="2">
-        <v>220.0</v>
+        <v>240.0</v>
       </c>
       <c r="P202" s="2">
-        <v>176.0</v>
+        <v>194.0</v>
       </c>
       <c r="Q202" s="2">
         <v>0.0</v>
@@ -14798,7 +14798,7 @@
         <v>1235.0</v>
       </c>
       <c r="J204" s="2">
-        <v>443.0</v>
+        <v>456.0</v>
       </c>
       <c r="K204" s="2">
         <v>1.0</v>
@@ -14810,13 +14810,13 @@
         <v>0.0</v>
       </c>
       <c r="N204" s="2">
-        <v>443.0</v>
+        <v>456.0</v>
       </c>
       <c r="O204" s="2">
-        <v>239.0</v>
+        <v>244.0</v>
       </c>
       <c r="P204" s="2">
-        <v>198.0</v>
+        <v>206.0</v>
       </c>
       <c r="Q204" s="2">
         <v>6.0</v>
@@ -14869,7 +14869,7 @@
         <v>897.0</v>
       </c>
       <c r="J205" s="2">
-        <v>374.0</v>
+        <v>389.0</v>
       </c>
       <c r="K205" s="2">
         <v>1.0</v>
@@ -14881,16 +14881,16 @@
         <v>0.0</v>
       </c>
       <c r="N205" s="2">
-        <v>374.0</v>
+        <v>389.0</v>
       </c>
       <c r="O205" s="2">
-        <v>176.0</v>
+        <v>179.0</v>
       </c>
       <c r="P205" s="2">
-        <v>169.0</v>
+        <v>179.0</v>
       </c>
       <c r="Q205" s="2">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="R205" s="2">
         <v>0.0</v>
@@ -14940,7 +14940,7 @@
         <v>859.0</v>
       </c>
       <c r="J206" s="2">
-        <v>648.0</v>
+        <v>660.0</v>
       </c>
       <c r="K206" s="2">
         <v>1.0</v>
@@ -14952,10 +14952,10 @@
         <v>0.0</v>
       </c>
       <c r="N206" s="2">
-        <v>648.0</v>
+        <v>660.0</v>
       </c>
       <c r="O206" s="2">
-        <v>389.0</v>
+        <v>401.0</v>
       </c>
       <c r="P206" s="2">
         <v>259.0</v>
@@ -15011,7 +15011,7 @@
         <v>943.0</v>
       </c>
       <c r="J207" s="2">
-        <v>441.0</v>
+        <v>447.0</v>
       </c>
       <c r="K207" s="2">
         <v>1.0</v>
@@ -15023,13 +15023,13 @@
         <v>0.0</v>
       </c>
       <c r="N207" s="2">
-        <v>441.0</v>
+        <v>447.0</v>
       </c>
       <c r="O207" s="2">
-        <v>249.0</v>
+        <v>253.0</v>
       </c>
       <c r="P207" s="2">
-        <v>188.0</v>
+        <v>190.0</v>
       </c>
       <c r="Q207" s="2">
         <v>4.0</v>
@@ -15082,7 +15082,7 @@
         <v>762.0</v>
       </c>
       <c r="J208" s="2">
-        <v>489.0</v>
+        <v>495.0</v>
       </c>
       <c r="K208" s="2">
         <v>1.0</v>
@@ -15094,16 +15094,16 @@
         <v>0.0</v>
       </c>
       <c r="N208" s="2">
-        <v>489.0</v>
+        <v>495.0</v>
       </c>
       <c r="O208" s="2">
         <v>123.0</v>
       </c>
       <c r="P208" s="2">
-        <v>215.0</v>
+        <v>216.0</v>
       </c>
       <c r="Q208" s="2">
-        <v>151.0</v>
+        <v>156.0</v>
       </c>
       <c r="R208" s="2">
         <v>0.0</v>
@@ -15153,7 +15153,7 @@
         <v>951.0</v>
       </c>
       <c r="J209" s="2">
-        <v>768.0</v>
+        <v>784.0</v>
       </c>
       <c r="K209" s="2">
         <v>1.0</v>
@@ -15165,13 +15165,13 @@
         <v>0.0</v>
       </c>
       <c r="N209" s="2">
-        <v>768.0</v>
+        <v>784.0</v>
       </c>
       <c r="O209" s="2">
-        <v>385.0</v>
+        <v>396.0</v>
       </c>
       <c r="P209" s="2">
-        <v>383.0</v>
+        <v>388.0</v>
       </c>
       <c r="Q209" s="2">
         <v>0.0</v>
@@ -15224,7 +15224,7 @@
         <v>792.0</v>
       </c>
       <c r="J210" s="2">
-        <v>603.0</v>
+        <v>606.0</v>
       </c>
       <c r="K210" s="2">
         <v>1.0</v>
@@ -15236,10 +15236,10 @@
         <v>0.0</v>
       </c>
       <c r="N210" s="2">
-        <v>603.0</v>
+        <v>606.0</v>
       </c>
       <c r="O210" s="2">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="P210" s="2">
         <v>301.0</v>
@@ -15295,7 +15295,7 @@
         <v>1074.0</v>
       </c>
       <c r="J211" s="2">
-        <v>786.0</v>
+        <v>810.0</v>
       </c>
       <c r="K211" s="2">
         <v>1.0</v>
@@ -15307,13 +15307,13 @@
         <v>0.0</v>
       </c>
       <c r="N211" s="2">
-        <v>786.0</v>
+        <v>810.0</v>
       </c>
       <c r="O211" s="2">
-        <v>403.0</v>
+        <v>415.0</v>
       </c>
       <c r="P211" s="2">
-        <v>383.0</v>
+        <v>395.0</v>
       </c>
       <c r="Q211" s="2">
         <v>0.0</v>
@@ -15437,7 +15437,7 @@
         <v>1034.0</v>
       </c>
       <c r="J213" s="2">
-        <v>596.0</v>
+        <v>599.0</v>
       </c>
       <c r="K213" s="2">
         <v>1.0</v>
@@ -15449,13 +15449,13 @@
         <v>0.0</v>
       </c>
       <c r="N213" s="2">
-        <v>596.0</v>
+        <v>599.0</v>
       </c>
       <c r="O213" s="2">
-        <v>306.0</v>
+        <v>307.0</v>
       </c>
       <c r="P213" s="2">
-        <v>290.0</v>
+        <v>292.0</v>
       </c>
       <c r="Q213" s="2">
         <v>0.0</v>
@@ -15579,7 +15579,7 @@
         <v>1067.0</v>
       </c>
       <c r="J215" s="2">
-        <v>680.0</v>
+        <v>689.0</v>
       </c>
       <c r="K215" s="2">
         <v>1.0</v>
@@ -15591,19 +15591,19 @@
         <v>0.0</v>
       </c>
       <c r="N215" s="2">
-        <v>680.0</v>
+        <v>689.0</v>
       </c>
       <c r="O215" s="2">
-        <v>274.0</v>
+        <v>278.0</v>
       </c>
       <c r="P215" s="2">
-        <v>406.0</v>
+        <v>411.0</v>
       </c>
       <c r="Q215" s="2">
         <v>0.0</v>
       </c>
       <c r="R215" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="S215" s="2">
         <v>9.0</v>
@@ -15612,13 +15612,13 @@
         <v>3.0</v>
       </c>
       <c r="U215" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V215" s="2">
         <v>0.0</v>
       </c>
       <c r="W215" s="2">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="216" ht="15.75" customHeight="1">
@@ -15650,7 +15650,7 @@
         <v>576.0</v>
       </c>
       <c r="J216" s="2">
-        <v>298.0</v>
+        <v>338.0</v>
       </c>
       <c r="K216" s="2">
         <v>1.0</v>
@@ -15662,13 +15662,13 @@
         <v>0.0</v>
       </c>
       <c r="N216" s="2">
-        <v>298.0</v>
+        <v>338.0</v>
       </c>
       <c r="O216" s="2">
-        <v>156.0</v>
+        <v>171.0</v>
       </c>
       <c r="P216" s="2">
-        <v>128.0</v>
+        <v>153.0</v>
       </c>
       <c r="Q216" s="2">
         <v>14.0</v>
@@ -15934,7 +15934,7 @@
         <v>867.0</v>
       </c>
       <c r="J220" s="2">
-        <v>566.0</v>
+        <v>584.0</v>
       </c>
       <c r="K220" s="2">
         <v>1.0</v>
@@ -15946,16 +15946,16 @@
         <v>0.0</v>
       </c>
       <c r="N220" s="2">
-        <v>566.0</v>
+        <v>584.0</v>
       </c>
       <c r="O220" s="2">
         <v>90.0</v>
       </c>
       <c r="P220" s="2">
-        <v>260.0</v>
+        <v>262.0</v>
       </c>
       <c r="Q220" s="2">
-        <v>216.0</v>
+        <v>232.0</v>
       </c>
       <c r="R220" s="2">
         <v>0.0</v>
@@ -16005,7 +16005,7 @@
         <v>848.0</v>
       </c>
       <c r="J221" s="2">
-        <v>555.0</v>
+        <v>605.0</v>
       </c>
       <c r="K221" s="2">
         <v>1.0</v>
@@ -16017,16 +16017,16 @@
         <v>1.0</v>
       </c>
       <c r="N221" s="2">
-        <v>554.0</v>
+        <v>604.0</v>
       </c>
       <c r="O221" s="2">
         <v>115.0</v>
       </c>
       <c r="P221" s="2">
-        <v>230.0</v>
+        <v>244.0</v>
       </c>
       <c r="Q221" s="2">
-        <v>210.0</v>
+        <v>246.0</v>
       </c>
       <c r="R221" s="2">
         <v>1.0</v>
@@ -16076,7 +16076,7 @@
         <v>1043.0</v>
       </c>
       <c r="J222" s="2">
-        <v>627.0</v>
+        <v>629.0</v>
       </c>
       <c r="K222" s="2">
         <v>1.0</v>
@@ -16088,16 +16088,16 @@
         <v>0.0</v>
       </c>
       <c r="N222" s="2">
-        <v>627.0</v>
+        <v>629.0</v>
       </c>
       <c r="O222" s="2">
         <v>126.0</v>
       </c>
       <c r="P222" s="2">
-        <v>266.0</v>
+        <v>267.0</v>
       </c>
       <c r="Q222" s="2">
-        <v>235.0</v>
+        <v>236.0</v>
       </c>
       <c r="R222" s="2">
         <v>0.0</v>
@@ -16147,7 +16147,7 @@
         <v>1272.0</v>
       </c>
       <c r="J223" s="2">
-        <v>708.0</v>
+        <v>711.0</v>
       </c>
       <c r="K223" s="2">
         <v>1.0</v>
@@ -16159,19 +16159,19 @@
         <v>0.0</v>
       </c>
       <c r="N223" s="2">
-        <v>708.0</v>
+        <v>711.0</v>
       </c>
       <c r="O223" s="2">
         <v>66.0</v>
       </c>
       <c r="P223" s="2">
-        <v>243.0</v>
+        <v>245.0</v>
       </c>
       <c r="Q223" s="2">
-        <v>399.0</v>
+        <v>400.0</v>
       </c>
       <c r="R223" s="2">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="S223" s="2">
         <v>0.0</v>
@@ -16186,7 +16186,7 @@
         <v>0.0</v>
       </c>
       <c r="W223" s="2">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="224" ht="15.75" customHeight="1">
@@ -16289,7 +16289,7 @@
         <v>1423.0</v>
       </c>
       <c r="J225" s="2">
-        <v>1261.0</v>
+        <v>1263.0</v>
       </c>
       <c r="K225" s="2">
         <v>1.0</v>
@@ -16301,10 +16301,10 @@
         <v>0.0</v>
       </c>
       <c r="N225" s="2">
-        <v>1261.0</v>
+        <v>1263.0</v>
       </c>
       <c r="O225" s="2">
-        <v>718.0</v>
+        <v>720.0</v>
       </c>
       <c r="P225" s="2">
         <v>543.0</v>
@@ -16313,10 +16313,10 @@
         <v>0.0</v>
       </c>
       <c r="R225" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="S225" s="2">
-        <v>4.0</v>
+        <v>20.0</v>
       </c>
       <c r="T225" s="2">
         <v>0.0</v>
@@ -16328,7 +16328,7 @@
         <v>0.0</v>
       </c>
       <c r="W225" s="2">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="226" ht="15.75" customHeight="1">
@@ -16360,7 +16360,7 @@
         <v>1256.0</v>
       </c>
       <c r="J226" s="2">
-        <v>624.0</v>
+        <v>685.0</v>
       </c>
       <c r="K226" s="2">
         <v>1.0</v>
@@ -16372,19 +16372,19 @@
         <v>0.0</v>
       </c>
       <c r="N226" s="2">
-        <v>624.0</v>
+        <v>685.0</v>
       </c>
       <c r="O226" s="2">
         <v>46.0</v>
       </c>
       <c r="P226" s="2">
-        <v>292.0</v>
+        <v>318.0</v>
       </c>
       <c r="Q226" s="2">
-        <v>286.0</v>
+        <v>321.0</v>
       </c>
       <c r="R226" s="2">
-        <v>116.0</v>
+        <v>120.0</v>
       </c>
       <c r="S226" s="2">
         <v>21.0</v>
@@ -16399,7 +16399,7 @@
         <v>0.0</v>
       </c>
       <c r="W226" s="2">
-        <v>137.0</v>
+        <v>141.0</v>
       </c>
     </row>
     <row r="227" ht="15.75" customHeight="1">
@@ -16502,7 +16502,7 @@
         <v>1402.0</v>
       </c>
       <c r="J228" s="2">
-        <v>626.0</v>
+        <v>629.0</v>
       </c>
       <c r="K228" s="2">
         <v>1.0</v>
@@ -16514,7 +16514,7 @@
         <v>0.0</v>
       </c>
       <c r="N228" s="2">
-        <v>626.0</v>
+        <v>629.0</v>
       </c>
       <c r="O228" s="2">
         <v>52.0</v>
@@ -16523,7 +16523,7 @@
         <v>264.0</v>
       </c>
       <c r="Q228" s="2">
-        <v>310.0</v>
+        <v>313.0</v>
       </c>
       <c r="R228" s="2">
         <v>0.0</v>
@@ -16742,7 +16742,7 @@
         <v>10.0</v>
       </c>
       <c r="S231" s="2">
-        <v>44.0</v>
+        <v>56.0</v>
       </c>
       <c r="T231" s="2">
         <v>1.0</v>
@@ -16754,7 +16754,7 @@
         <v>0.0</v>
       </c>
       <c r="W231" s="2">
-        <v>58.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="232" ht="15.75" customHeight="1">
@@ -16786,7 +16786,7 @@
         <v>1369.0</v>
       </c>
       <c r="J232" s="2">
-        <v>570.0</v>
+        <v>607.0</v>
       </c>
       <c r="K232" s="2">
         <v>1.0</v>
@@ -16798,16 +16798,16 @@
         <v>0.0</v>
       </c>
       <c r="N232" s="2">
-        <v>570.0</v>
+        <v>607.0</v>
       </c>
       <c r="O232" s="2">
         <v>5.0</v>
       </c>
       <c r="P232" s="2">
-        <v>101.0</v>
+        <v>118.0</v>
       </c>
       <c r="Q232" s="2">
-        <v>464.0</v>
+        <v>484.0</v>
       </c>
       <c r="R232" s="2">
         <v>1.0</v>
@@ -16857,7 +16857,7 @@
         <v>666.0</v>
       </c>
       <c r="J233" s="2">
-        <v>427.0</v>
+        <v>438.0</v>
       </c>
       <c r="K233" s="2">
         <v>1.0</v>
@@ -16869,16 +16869,16 @@
         <v>0.0</v>
       </c>
       <c r="N233" s="2">
-        <v>427.0</v>
+        <v>438.0</v>
       </c>
       <c r="O233" s="2">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="P233" s="2">
-        <v>211.0</v>
+        <v>215.0</v>
       </c>
       <c r="Q233" s="2">
-        <v>135.0</v>
+        <v>141.0</v>
       </c>
       <c r="R233" s="2">
         <v>3.0</v>
